--- a/AAAGameData/DataTables/BuffTable.xlsx
+++ b/AAAGameData/DataTables/BuffTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="77">
   <si>
     <t>#</t>
   </si>
@@ -240,6 +240,24 @@
   </si>
   <si>
     <t>敌人持续流血6秒，每秒损失10%最大生命值</t>
+  </si>
+  <si>
+    <t>战意激昂</t>
+  </si>
+  <si>
+    <t>攻击速度提升20%，伤害提升15%，持续10秒</t>
+  </si>
+  <si>
+    <t>{"AtkSpeed":"20%","AtkDamage":"15%"}</t>
+  </si>
+  <si>
+    <t>狂怒之心</t>
+  </si>
+  <si>
+    <t>全体友方伤害提升15%；召唤师自身伤害提升30%（战场有友方HP低于50%时持续生效）</t>
+  </si>
+  <si>
+    <t>{"SummonerAtkDamage":"30%"}</t>
   </si>
 </sst>
 </file>
@@ -1211,20 +1229,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="44" customWidth="1"/>
+    <col min="6" max="6" width="71.625" customWidth="1"/>
     <col min="7" max="7" width="48" customWidth="1"/>
     <col min="8" max="8" width="50" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="50" customWidth="1"/>
-    <col min="11" max="11" width="38.75" customWidth="1"/>
-    <col min="12" max="13" width="50" customWidth="1"/>
+    <col min="10" max="13" width="50" customWidth="1"/>
     <col min="14" max="14" width="44" customWidth="1"/>
     <col min="15" max="15" width="42" customWidth="1"/>
     <col min="16" max="16" width="50" customWidth="1"/>
@@ -2115,6 +2131,114 @@
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
     </row>
+    <row r="18" ht="15" customHeight="1" spans="1:23">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1">
+        <v>4001</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="1">
+        <v>14001</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1">
+        <v>10</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>1</v>
+      </c>
+      <c r="O18" s="1">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:23">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1">
+        <v>4003</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="1">
+        <v>14003</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1">
+        <v>5</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
+        <v>1</v>
+      </c>
+      <c r="O19" s="1">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>0</v>
+      </c>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/AAAGameData/DataTables/BuffTable.xlsx
+++ b/AAAGameData/DataTables/BuffTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="27948" windowHeight="11855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="79">
   <si>
     <t>#</t>
   </si>
@@ -258,6 +258,12 @@
   </si>
   <si>
     <t>{"SummonerAtkDamage":"30%"}</t>
+  </si>
+  <si>
+    <t>暗影咒体</t>
+  </si>
+  <si>
+    <t>暂无</t>
   </si>
 </sst>
 </file>
@@ -270,14 +276,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -733,148 +732,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1229,14 +1228,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:W20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="71.625" customWidth="1"/>
+    <col min="6" max="6" width="71.6296296296296" customWidth="1"/>
     <col min="7" max="7" width="48" customWidth="1"/>
     <col min="8" max="8" width="50" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
@@ -1391,7 +1390,7 @@
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
     </row>
-    <row r="4" ht="54" spans="1:23">
+    <row r="4" ht="57.6" spans="1:23">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2141,7 +2140,7 @@
         <v>71</v>
       </c>
       <c r="E18" s="1">
-        <v>14001</v>
+        <v>10201</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>72</v>
@@ -2187,14 +2186,14 @@
     <row r="19" ht="15" customHeight="1" spans="1:23">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
         <v>74</v>
       </c>
       <c r="E19" s="1">
-        <v>14003</v>
+        <v>10202</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>75</v>
@@ -2239,6 +2238,47 @@
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
     </row>
+    <row r="20" spans="1:23">
+      <c r="B20">
+        <v>4003</v>
+      </c>
+      <c r="D20" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20">
+        <v>10203</v>
+      </c>
+      <c r="F20" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/AAAGameData/DataTables/BuffTable.xlsx
+++ b/AAAGameData/DataTables/BuffTable.xlsx
@@ -1515,7 +1515,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M5" s="1">
         <v>1</v>
@@ -1560,7 +1560,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M8" s="1">
         <v>0</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M10" s="1">
         <v>0</v>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M13" s="1">
         <v>0</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M14" s="1">
         <v>0</v>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15" s="1">
         <v>0</v>
@@ -2028,7 +2028,7 @@
         <v>68</v>
       </c>
       <c r="L16" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M16" s="1">
         <v>0</v>
@@ -2073,7 +2073,7 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M17" s="1">
         <v>1</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M18" s="1">
         <v>0</v>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M21" s="1">
         <v>0</v>
@@ -2306,7 +2306,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M22" s="1">
         <v>1</v>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M23" s="1">
         <v>0</v>
@@ -2400,7 +2400,7 @@
         <v>68</v>
       </c>
       <c r="L24" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" s="1">
         <v>0</v>
@@ -2447,7 +2447,7 @@
         <v>91</v>
       </c>
       <c r="L25" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M25" s="1">
         <v>0</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M26" s="1">
         <v>0</v>
@@ -2541,7 +2541,7 @@
         <v>97</v>
       </c>
       <c r="L27" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M27" s="1">
         <v>0</v>

--- a/AAAGameData/DataTables/BuffTable.xlsx
+++ b/AAAGameData/DataTables/BuffTable.xlsx
@@ -1515,7 +1515,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M5" s="1">
         <v>1</v>
@@ -1560,7 +1560,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M8" s="1">
         <v>0</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M10" s="1">
         <v>0</v>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M13" s="1">
         <v>0</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M14" s="1">
         <v>0</v>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" s="1">
         <v>0</v>
@@ -2028,7 +2028,7 @@
         <v>68</v>
       </c>
       <c r="L16" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M16" s="1">
         <v>0</v>
@@ -2073,7 +2073,7 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M17" s="1">
         <v>1</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M18" s="1">
         <v>0</v>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M21" s="1">
         <v>0</v>
@@ -2306,7 +2306,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M22" s="1">
         <v>1</v>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M23" s="1">
         <v>0</v>
@@ -2400,7 +2400,7 @@
         <v>68</v>
       </c>
       <c r="L24" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" s="1">
         <v>0</v>
@@ -2447,7 +2447,7 @@
         <v>91</v>
       </c>
       <c r="L25" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M25" s="1">
         <v>0</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M26" s="1">
         <v>0</v>
@@ -2541,7 +2541,7 @@
         <v>97</v>
       </c>
       <c r="L27" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M27" s="1">
         <v>0</v>

--- a/AAAGameData/DataTables/BuffTable.xlsx
+++ b/AAAGameData/DataTables/BuffTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="27948" windowHeight="11855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -266,7 +266,7 @@
     <t>暂无</t>
   </si>
   <si>
-    <t>神圣庇护·护盾</t>
+    <t>神圣庇护</t>
   </si>
   <si>
     <t>提供100点护盾，持续5秒</t>
@@ -296,7 +296,7 @@
     <t>眩晕2秒，无法行动</t>
   </si>
   <si>
-    <t>冰霜新星·冰冻</t>
+    <t>冰霜新星</t>
   </si>
   <si>
     <t>冰冻3秒，无法行动</t>
@@ -314,7 +314,7 @@
     <t>{"AtkDamage":"80%","Armor":"-30%"}</t>
   </si>
   <si>
-    <t>混乱诅咒·混乱</t>
+    <t>混乱诅咒</t>
   </si>
   <si>
     <t>陷入混乱4秒，有概率攻击队友</t>
@@ -333,14 +333,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -796,148 +789,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1293,7 +1286,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Q27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -1435,7 +1428,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="54" spans="1:17">
+    <row r="4" ht="57.6" spans="1:17">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2515,14 +2508,14 @@
     <row r="27" ht="15" customHeight="1" spans="1:17">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
-        <v>5010</v>
+        <v>5009</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E27" s="1">
-        <v>15010</v>
+        <v>15009</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>96</v>

--- a/AAAGameData/DataTables/BuffTable.xlsx
+++ b/AAAGameData/DataTables/BuffTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="11855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -53,9 +53,6 @@
     <t>EffectType</t>
   </si>
   <si>
-    <t>EffectValue</t>
-  </si>
-  <si>
     <t>StatMods</t>
   </si>
   <si>
@@ -110,9 +107,6 @@
     <t>效果类型：1 : 属性修改 (按比例/数值修改攻击、防御、速度等)2 : 周期性 (DOT/HOT，如流血、回春)3 : 护盾 (吸收伤害)4 : 状态改变 (控制类：眩晕、冰冻、沉默)5 : 特殊逻辑 (通过代码触发特定事件)</t>
   </si>
   <si>
-    <t>效果数值</t>
-  </si>
-  <si>
     <t>属性修改参数(JSON)：例如 {"AtkDamage":"25%","AtkRange":"30%"}；值为数值表示固定增量，带%表示按当前属性百分比计算</t>
   </si>
   <si>
@@ -143,6 +137,9 @@
     <t>每秒每层造成5点伤害，5/10层减50物抗</t>
   </si>
   <si>
+    <t>{"DamagePerStack":5}</t>
+  </si>
+  <si>
     <t>寒霜</t>
   </si>
   <si>
@@ -242,6 +239,9 @@
     <t>敌人持续流血6秒，每秒损失10%最大生命值</t>
   </si>
   <si>
+    <t>{"DamageRatio":0.1}</t>
+  </si>
+  <si>
     <t>战意激昂</t>
   </si>
   <si>
@@ -269,10 +269,10 @@
     <t>神圣庇护</t>
   </si>
   <si>
-    <t>提供100点护盾，持续5秒</t>
-  </si>
-  <si>
-    <t>{"Shield":100}</t>
+    <t>提供1000点护盾，持续30秒</t>
+  </si>
+  <si>
+    <t>{"Shield":1000}</t>
   </si>
   <si>
     <t>烈焰风暴·灼烧</t>
@@ -1285,8 +1285,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:P27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -1294,16 +1294,14 @@
     <col min="4" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="50" customWidth="1"/>
     <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="13" width="50" customWidth="1"/>
-    <col min="14" max="14" width="44" customWidth="1"/>
-    <col min="15" max="15" width="42" customWidth="1"/>
-    <col min="16" max="16" width="50" customWidth="1"/>
-    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="8" max="12" width="50" customWidth="1"/>
+    <col min="13" max="13" width="44" customWidth="1"/>
+    <col min="14" max="14" width="42" customWidth="1"/>
+    <col min="15" max="15" width="50" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1324,9 +1322,8 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-    </row>
-    <row r="2" spans="1:17">
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1373,128 +1370,119 @@
       <c r="P2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="54" spans="1:16">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="57.6" spans="1:17">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:16">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1">
         <v>1401</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G5" s="1">
         <v>2</v>
@@ -1502,19 +1490,21 @@
       <c r="H5" s="1">
         <v>2</v>
       </c>
-      <c r="I5" s="1">
-        <v>5</v>
-      </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="1">
+        <v>10</v>
+      </c>
       <c r="L5" s="1">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1">
         <v>10</v>
       </c>
-      <c r="M5" s="1">
-        <v>1</v>
-      </c>
       <c r="N5" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O5" s="1">
         <v>0</v>
@@ -1522,24 +1512,21 @@
       <c r="P5" s="1">
         <v>0</v>
       </c>
-      <c r="Q5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:16">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1">
         <v>1402</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G6" s="1">
         <v>2</v>
@@ -1547,19 +1534,19 @@
       <c r="H6" s="1">
         <v>1</v>
       </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
+      <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
+      <c r="K6" s="1">
+        <v>10</v>
+      </c>
       <c r="L6" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -1567,24 +1554,21 @@
       <c r="P6" s="1">
         <v>0</v>
       </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:16">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" s="1">
         <v>1403</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -1592,19 +1576,19 @@
       <c r="H7" s="1">
         <v>5</v>
       </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
+      <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
       <c r="L7" s="1">
         <v>0</v>
       </c>
       <c r="M7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -1612,46 +1596,43 @@
       <c r="P7" s="1">
         <v>0</v>
       </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:16">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" s="1">
         <v>1404</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="1">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1">
+        <v>8</v>
+      </c>
       <c r="L8" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="1">
         <v>0</v>
@@ -1659,46 +1640,43 @@
       <c r="P8" s="1">
         <v>0</v>
       </c>
-      <c r="Q8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:16">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1">
         <v>1405</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="1">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1">
-        <v>1</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
       <c r="L9" s="1">
         <v>0</v>
       </c>
       <c r="M9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -1706,24 +1684,21 @@
       <c r="P9" s="1">
         <v>0</v>
       </c>
-      <c r="Q9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:16">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>6</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" s="1">
         <v>1406</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G10" s="1">
         <v>2</v>
@@ -1731,21 +1706,21 @@
       <c r="H10" s="1">
         <v>1</v>
       </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K10" s="1"/>
+      <c r="I10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1">
+        <v>4</v>
+      </c>
       <c r="L10" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -1753,46 +1728,43 @@
       <c r="P10" s="1">
         <v>0</v>
       </c>
-      <c r="Q10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:16">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>2001</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E11" s="1">
         <v>10001</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="1">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1">
-        <v>1</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
       <c r="L11" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="1">
         <v>0</v>
@@ -1800,46 +1772,43 @@
       <c r="P11" s="1">
         <v>0</v>
       </c>
-      <c r="Q11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:16">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>2002</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" s="1">
         <v>10002</v>
       </c>
       <c r="F12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="1">
-        <v>1</v>
-      </c>
-      <c r="H12" s="1">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1">
+        <v>10</v>
+      </c>
       <c r="L12" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="1">
         <v>0</v>
@@ -1847,46 +1816,43 @@
       <c r="P12" s="1">
         <v>0</v>
       </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:16">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>2003</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" s="1">
         <v>10003</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G13" s="1">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1">
-        <v>1</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="K13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1">
+        <v>8</v>
+      </c>
       <c r="L13" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="1">
         <v>0</v>
@@ -1894,46 +1860,43 @@
       <c r="P13" s="1">
         <v>0</v>
       </c>
-      <c r="Q13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:16">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>2004</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" s="1">
         <v>10004</v>
       </c>
       <c r="F14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G14" s="1">
-        <v>1</v>
-      </c>
-      <c r="H14" s="1">
-        <v>1</v>
-      </c>
-      <c r="I14" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="K14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1">
+        <v>10</v>
+      </c>
       <c r="L14" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="1">
         <v>0</v>
@@ -1941,24 +1904,21 @@
       <c r="P14" s="1">
         <v>0</v>
       </c>
-      <c r="Q14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:16">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>3001</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E15" s="1">
         <v>10101</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
@@ -1966,21 +1926,21 @@
       <c r="H15" s="1">
         <v>1</v>
       </c>
-      <c r="I15" s="1">
-        <v>-0.3</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K15" s="1"/>
+      <c r="I15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1">
+        <v>2</v>
+      </c>
       <c r="L15" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="1">
         <v>0</v>
@@ -1988,24 +1948,21 @@
       <c r="P15" s="1">
         <v>0</v>
       </c>
-      <c r="Q15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:16">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>3002</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E16" s="1">
         <v>10102</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G16" s="1">
         <v>2</v>
@@ -2013,21 +1970,21 @@
       <c r="H16" s="1">
         <v>4</v>
       </c>
-      <c r="I16" s="1">
-        <v>1</v>
-      </c>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1" t="s">
-        <v>68</v>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0.8</v>
       </c>
       <c r="L16" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
@@ -2035,24 +1992,21 @@
       <c r="P16" s="1">
         <v>0</v>
       </c>
-      <c r="Q16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:16">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>3003</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E17" s="1">
         <v>10103</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G17" s="1">
         <v>2</v>
@@ -2060,19 +2014,21 @@
       <c r="H17" s="1">
         <v>2</v>
       </c>
-      <c r="I17" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K17" s="1">
+        <v>6</v>
+      </c>
       <c r="L17" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M17" s="1">
         <v>1</v>
       </c>
       <c r="N17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="1">
         <v>0</v>
@@ -2080,11 +2036,8 @@
       <c r="P17" s="1">
         <v>0</v>
       </c>
-      <c r="Q17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:16">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>4001</v>
@@ -2105,21 +2058,21 @@
       <c r="H18" s="1">
         <v>1</v>
       </c>
-      <c r="I18" s="1">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="K18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1">
+        <v>10</v>
+      </c>
       <c r="L18" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="1">
         <v>0</v>
@@ -2127,11 +2080,8 @@
       <c r="P18" s="1">
         <v>0</v>
       </c>
-      <c r="Q18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:16">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>4002</v>
@@ -2152,23 +2102,23 @@
       <c r="H19" s="1">
         <v>5</v>
       </c>
-      <c r="I19" s="1">
-        <v>0</v>
+      <c r="I19" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K19" s="1" t="s">
         <v>76</v>
       </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
       <c r="L19" s="1">
         <v>0</v>
       </c>
       <c r="M19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" s="1">
         <v>0</v>
@@ -2176,11 +2126,8 @@
       <c r="P19" s="1">
         <v>0</v>
       </c>
-      <c r="Q19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:16">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>4003</v>
@@ -2201,19 +2148,19 @@
       <c r="H20" s="1">
         <v>5</v>
       </c>
-      <c r="I20" s="1">
-        <v>0</v>
-      </c>
+      <c r="I20" s="1"/>
       <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
       <c r="L20" s="1">
         <v>0</v>
       </c>
       <c r="M20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="1">
         <v>0</v>
@@ -2221,11 +2168,8 @@
       <c r="P20" s="1">
         <v>0</v>
       </c>
-      <c r="Q20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:16">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>5001</v>
@@ -2244,23 +2188,23 @@
         <v>1</v>
       </c>
       <c r="H21" s="1">
-        <v>1</v>
-      </c>
-      <c r="I21" s="1">
-        <v>0</v>
-      </c>
-      <c r="J21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1">
+        <v>30</v>
+      </c>
       <c r="L21" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" s="1">
         <v>0</v>
@@ -2268,11 +2212,8 @@
       <c r="P21" s="1">
         <v>0</v>
       </c>
-      <c r="Q21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:16">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>5002</v>
@@ -2293,19 +2234,21 @@
       <c r="H22" s="1">
         <v>2</v>
       </c>
-      <c r="I22" s="1">
+      <c r="I22" s="1"/>
+      <c r="J22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K22" s="1">
+        <v>3</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
+      <c r="M22" s="1">
         <v>5</v>
       </c>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1">
-        <v>3</v>
-      </c>
-      <c r="M22" s="1">
-        <v>1</v>
-      </c>
       <c r="N22" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -2313,11 +2256,8 @@
       <c r="P22" s="1">
         <v>0</v>
       </c>
-      <c r="Q22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="1:16">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>5003</v>
@@ -2338,21 +2278,21 @@
       <c r="H23" s="1">
         <v>1</v>
       </c>
-      <c r="I23" s="1">
-        <v>0</v>
-      </c>
-      <c r="J23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="K23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1">
+        <v>8</v>
+      </c>
       <c r="L23" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="1">
         <v>0</v>
@@ -2360,11 +2300,8 @@
       <c r="P23" s="1">
         <v>0</v>
       </c>
-      <c r="Q23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:16">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>5005</v>
@@ -2385,21 +2322,21 @@
       <c r="H24" s="1">
         <v>4</v>
       </c>
-      <c r="I24" s="1">
-        <v>1</v>
-      </c>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1" t="s">
-        <v>68</v>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K24" s="1">
+        <v>2</v>
       </c>
       <c r="L24" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" s="1">
         <v>0</v>
@@ -2407,11 +2344,8 @@
       <c r="P24" s="1">
         <v>0</v>
       </c>
-      <c r="Q24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:16">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>5007</v>
@@ -2432,21 +2366,21 @@
       <c r="H25" s="1">
         <v>4</v>
       </c>
-      <c r="I25" s="1">
-        <v>1</v>
-      </c>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1" t="s">
+      <c r="I25" s="1"/>
+      <c r="J25" s="1" t="s">
         <v>91</v>
       </c>
+      <c r="K25" s="1">
+        <v>3</v>
+      </c>
       <c r="L25" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="1">
         <v>0</v>
@@ -2454,11 +2388,8 @@
       <c r="P25" s="1">
         <v>0</v>
       </c>
-      <c r="Q25" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:16">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>5008</v>
@@ -2479,21 +2410,21 @@
       <c r="H26" s="1">
         <v>1</v>
       </c>
-      <c r="I26" s="1">
-        <v>0</v>
-      </c>
-      <c r="J26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="K26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1">
+        <v>10</v>
+      </c>
       <c r="L26" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="1">
         <v>0</v>
@@ -2501,11 +2432,8 @@
       <c r="P26" s="1">
         <v>0</v>
       </c>
-      <c r="Q26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" spans="1:17">
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:16">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>5009</v>
@@ -2526,29 +2454,26 @@
       <c r="H27" s="1">
         <v>4</v>
       </c>
-      <c r="I27" s="1">
-        <v>1</v>
-      </c>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1" t="s">
+      <c r="I27" s="1"/>
+      <c r="J27" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="K27" s="1">
+        <v>4</v>
+      </c>
       <c r="L27" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" s="1">
         <v>0</v>
       </c>
       <c r="P27" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="1">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/BuffTable.xlsx
+++ b/AAAGameData/DataTables/BuffTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="126">
   <si>
     <t>#</t>
   </si>
@@ -275,12 +275,6 @@
     <t>{"Shield":1000}</t>
   </si>
   <si>
-    <t>烈焰风暴·灼烧</t>
-  </si>
-  <si>
-    <t>每秒每层造成5点伤害，最多5层，持续3秒</t>
-  </si>
-  <si>
     <t>战争号角</t>
   </si>
   <si>
@@ -321,6 +315,96 @@
   </si>
   <si>
     <t>{"SpecialState":"Confused"}</t>
+  </si>
+  <si>
+    <t>反伤之盾</t>
+  </si>
+  <si>
+    <t>返回受到伤害的30%，持续10秒</t>
+  </si>
+  <si>
+    <t>{"reflectDamageRatio":0.3}</t>
+  </si>
+  <si>
+    <t>圣域防线</t>
+  </si>
+  <si>
+    <t>护甲提升30%，持续10秒</t>
+  </si>
+  <si>
+    <t>{"Armor":"30%"}</t>
+  </si>
+  <si>
+    <t>护盾再生</t>
+  </si>
+  <si>
+    <t>每3秒恢复50点护盾，持续15秒</t>
+  </si>
+  <si>
+    <t>{"ShieldRegenPerSecond":50}</t>
+  </si>
+  <si>
+    <t>血源强化</t>
+  </si>
+  <si>
+    <t>最大生命值提升30%，持续15秒</t>
+  </si>
+  <si>
+    <t>{"MaxHP":"30%"}</t>
+  </si>
+  <si>
+    <t>吸血之刃</t>
+  </si>
+  <si>
+    <t>对敌方造成伤害时吸血40%</t>
+  </si>
+  <si>
+    <t>{"lifestealRatio":0.4}</t>
+  </si>
+  <si>
+    <t>护甲破碎</t>
+  </si>
+  <si>
+    <t>护甲降低5点，持续15秒</t>
+  </si>
+  <si>
+    <t>{"Armor":"-5"}</t>
+  </si>
+  <si>
+    <t>虚弱诅咒</t>
+  </si>
+  <si>
+    <t>攻击力降低30%，持续15秒</t>
+  </si>
+  <si>
+    <t>{"AtkDamage":"-30%"}</t>
+  </si>
+  <si>
+    <t>沉默之符</t>
+  </si>
+  <si>
+    <t>禁用技能，持续10秒</t>
+  </si>
+  <si>
+    <t>{"SpecialState":"Silence"}</t>
+  </si>
+  <si>
+    <t>嘲讽之声</t>
+  </si>
+  <si>
+    <t>强制攻击目标，持续10秒</t>
+  </si>
+  <si>
+    <t>{"SpecialState":"Taunt"}</t>
+  </si>
+  <si>
+    <t>剧毒之雾</t>
+  </si>
+  <si>
+    <t>每秒损失5%最大生命值，持续15秒</t>
+  </si>
+  <si>
+    <t>{"DamageRatio":0.05}</t>
   </si>
 </sst>
 </file>
@@ -333,7 +417,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -789,148 +880,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1285,8 +1376,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:P38"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -1419,7 +1510,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" ht="54" spans="1:16">
+    <row r="4" ht="57.6" spans="1:16">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2216,36 +2307,36 @@
     <row r="22" ht="15" customHeight="1" spans="1:16">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
-        <v>5002</v>
+        <v>5003</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E22" s="1">
-        <v>15002</v>
+        <v>15003</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>83</v>
       </c>
       <c r="G22" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="1">
-        <v>2</v>
-      </c>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J22" s="1"/>
       <c r="K22" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N22" s="1">
         <v>0</v>
@@ -2260,30 +2351,30 @@
     <row r="23" ht="15" customHeight="1" spans="1:16">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
-        <v>5003</v>
+        <v>5005</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E23" s="1">
-        <v>15003</v>
+        <v>15005</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G23" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="1">
-        <v>1</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J23" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="K23" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L23" s="1">
         <v>0</v>
@@ -2304,14 +2395,14 @@
     <row r="24" ht="15" customHeight="1" spans="1:16">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
-        <v>5005</v>
+        <v>5007</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
         <v>87</v>
       </c>
       <c r="E24" s="1">
-        <v>15005</v>
+        <v>15007</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>88</v>
@@ -2324,10 +2415,10 @@
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="K24" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L24" s="1">
         <v>0</v>
@@ -2348,30 +2439,30 @@
     <row r="25" ht="15" customHeight="1" spans="1:16">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
-        <v>5007</v>
+        <v>5008</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E25" s="1">
-        <v>15007</v>
+        <v>15008</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G25" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" s="1">
-        <v>4</v>
-      </c>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1" t="s">
-        <v>91</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J25" s="1"/>
       <c r="K25" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L25" s="1">
         <v>0</v>
@@ -2392,30 +2483,30 @@
     <row r="26" ht="15" customHeight="1" spans="1:16">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
-        <v>5008</v>
+        <v>5009</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E26" s="1">
-        <v>15008</v>
+        <v>15009</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="1">
-        <v>1</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="J26" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="K26" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L26" s="1">
         <v>0</v>
@@ -2436,46 +2527,478 @@
     <row r="27" ht="15" customHeight="1" spans="1:16">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
-        <v>5009</v>
+        <v>5011</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E27" s="1">
-        <v>15009</v>
+        <v>15011</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G27" s="1">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1">
+        <v>5</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1">
+        <v>10</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>1</v>
+      </c>
+      <c r="N27" s="1">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1">
+        <v>0</v>
+      </c>
+      <c r="P27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="1:16">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1">
+        <v>5012</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" s="1">
+        <v>15012</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1">
+        <v>10</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>1</v>
+      </c>
+      <c r="N28" s="1">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1">
+        <v>0</v>
+      </c>
+      <c r="P28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="1:16">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1">
+        <v>5013</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="1">
+        <v>15013</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1">
         <v>2</v>
       </c>
-      <c r="H27" s="1">
+      <c r="I29" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1">
+        <v>15</v>
+      </c>
+      <c r="L29" s="1">
+        <v>3</v>
+      </c>
+      <c r="M29" s="1">
+        <v>1</v>
+      </c>
+      <c r="N29" s="1">
+        <v>0</v>
+      </c>
+      <c r="O29" s="1">
+        <v>0</v>
+      </c>
+      <c r="P29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" spans="1:16">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1">
+        <v>5014</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30" s="1">
+        <v>15014</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1">
+        <v>15</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>1</v>
+      </c>
+      <c r="N30" s="1">
+        <v>0</v>
+      </c>
+      <c r="O30" s="1">
+        <v>0</v>
+      </c>
+      <c r="P30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" spans="1:16">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1">
+        <v>5015</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E31" s="1">
+        <v>15015</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G31" s="1">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1">
+        <v>5</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>1</v>
+      </c>
+      <c r="N31" s="1">
+        <v>0</v>
+      </c>
+      <c r="O31" s="1">
+        <v>0</v>
+      </c>
+      <c r="P31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" spans="1:16">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1">
+        <v>5017</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E32" s="1">
+        <v>15017</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G32" s="1">
+        <v>2</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1">
+        <v>15</v>
+      </c>
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
+        <v>1</v>
+      </c>
+      <c r="N32" s="1">
+        <v>0</v>
+      </c>
+      <c r="O32" s="1">
+        <v>0</v>
+      </c>
+      <c r="P32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" spans="1:16">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1">
+        <v>5018</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E33" s="1">
+        <v>15018</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2</v>
+      </c>
+      <c r="H33" s="1">
+        <v>1</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1">
+        <v>15</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
+        <v>1</v>
+      </c>
+      <c r="N33" s="1">
+        <v>0</v>
+      </c>
+      <c r="O33" s="1">
+        <v>0</v>
+      </c>
+      <c r="P33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" spans="1:16">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1">
+        <v>5019</v>
+      </c>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E34" s="1">
+        <v>15019</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G34" s="1">
+        <v>2</v>
+      </c>
+      <c r="H34" s="1">
         <v>4</v>
       </c>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K27" s="1">
+      <c r="I34" s="1"/>
+      <c r="J34" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="K34" s="1">
+        <v>10</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1">
+        <v>1</v>
+      </c>
+      <c r="N34" s="1">
+        <v>0</v>
+      </c>
+      <c r="O34" s="1">
+        <v>0</v>
+      </c>
+      <c r="P34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" spans="1:16">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1">
+        <v>5020</v>
+      </c>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E35" s="1">
+        <v>15020</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G35" s="1">
+        <v>2</v>
+      </c>
+      <c r="H35" s="1">
         <v>4</v>
       </c>
-      <c r="L27" s="1">
-        <v>0</v>
-      </c>
-      <c r="M27" s="1">
-        <v>1</v>
-      </c>
-      <c r="N27" s="1">
-        <v>0</v>
-      </c>
-      <c r="O27" s="1">
-        <v>0</v>
-      </c>
-      <c r="P27" s="1">
-        <v>0</v>
-      </c>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K35" s="1">
+        <v>10</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+      <c r="M35" s="1">
+        <v>1</v>
+      </c>
+      <c r="N35" s="1">
+        <v>0</v>
+      </c>
+      <c r="O35" s="1">
+        <v>0</v>
+      </c>
+      <c r="P35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" spans="1:16">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1">
+        <v>5021</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E36" s="1">
+        <v>15021</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G36" s="1">
+        <v>2</v>
+      </c>
+      <c r="H36" s="1">
+        <v>2</v>
+      </c>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K36" s="1">
+        <v>15</v>
+      </c>
+      <c r="L36" s="1">
+        <v>1</v>
+      </c>
+      <c r="M36" s="1">
+        <v>1</v>
+      </c>
+      <c r="N36" s="1">
+        <v>0</v>
+      </c>
+      <c r="O36" s="1">
+        <v>0</v>
+      </c>
+      <c r="P36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" spans="1:16">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+    </row>
+    <row r="38" ht="15" customHeight="1" spans="1:16">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AAAGameData/DataTables/BuffTable.xlsx
+++ b/AAAGameData/DataTables/BuffTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -417,14 +417,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -880,148 +873,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1377,7 +1370,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -1385,7 +1378,8 @@
     <col min="4" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="50" customWidth="1"/>
     <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="12" width="50" customWidth="1"/>
+    <col min="8" max="8" width="28.25" customWidth="1"/>
+    <col min="9" max="12" width="50" customWidth="1"/>
     <col min="13" max="13" width="44" customWidth="1"/>
     <col min="14" max="14" width="42" customWidth="1"/>
     <col min="15" max="15" width="50" customWidth="1"/>
@@ -1510,7 +1504,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" ht="57.6" spans="1:16">
+    <row r="4" ht="54" spans="1:16">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>

--- a/AAAGameData/DataTables/BuffTable.xlsx
+++ b/AAAGameData/DataTables/BuffTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="27948" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="132">
   <si>
     <t>#</t>
   </si>
@@ -177,6 +177,24 @@
   </si>
   <si>
     <t>{"MoveSpeed":"-30%","AtkSpeed":"-15%"}</t>
+  </si>
+  <si>
+    <t>腐蚀</t>
+  </si>
+  <si>
+    <t>每层降低15%护甲和魔抗，持续6s，最多2层</t>
+  </si>
+  <si>
+    <t>黑暗狂暴</t>
+  </si>
+  <si>
+    <t>攻速+30%，持续5s</t>
+  </si>
+  <si>
+    <t>恐惧</t>
+  </si>
+  <si>
+    <t>攻击力-20%，持续2s</t>
   </si>
   <si>
     <t>先手·速度爆发</t>
@@ -417,7 +435,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -873,148 +898,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1369,8 +1394,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:P39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -1378,8 +1403,7 @@
     <col min="4" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="50" customWidth="1"/>
     <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="28.25" customWidth="1"/>
-    <col min="9" max="12" width="50" customWidth="1"/>
+    <col min="8" max="12" width="50" customWidth="1"/>
     <col min="13" max="13" width="44" customWidth="1"/>
     <col min="14" max="14" width="42" customWidth="1"/>
     <col min="15" max="15" width="50" customWidth="1"/>
@@ -1504,7 +1528,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" ht="54" spans="1:16">
+    <row r="4" ht="57.6" spans="1:16">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1817,36 +1841,34 @@
     <row r="11" ht="15" customHeight="1" spans="1:16">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
-        <v>2001</v>
+        <v>7</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E11" s="1">
-        <v>10001</v>
+        <v>1407</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>51</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="1">
         <v>1</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L11" s="1">
         <v>0</v>
       </c>
       <c r="M11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" s="1">
         <v>0</v>
@@ -1861,30 +1883,28 @@
     <row r="12" ht="15" customHeight="1" spans="1:16">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
-        <v>2002</v>
+        <v>8</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1408</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="1">
-        <v>10002</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="G12" s="1">
         <v>1</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
@@ -1905,30 +1925,28 @@
     <row r="13" ht="15" customHeight="1" spans="1:16">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
-        <v>2003</v>
+        <v>9</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E13" s="1">
-        <v>10003</v>
+        <v>1409</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G13" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="1">
         <v>1</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L13" s="1">
         <v>0</v>
@@ -1949,17 +1967,17 @@
     <row r="14" ht="15" customHeight="1" spans="1:16">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E14" s="1">
-        <v>10004</v>
+        <v>10001</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -1968,11 +1986,11 @@
         <v>1</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L14" s="1">
         <v>0</v>
@@ -1993,30 +2011,30 @@
     <row r="15" ht="15" customHeight="1" spans="1:16">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
-        <v>3001</v>
+        <v>2002</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E15" s="1">
-        <v>10101</v>
+        <v>10002</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="1">
         <v>1</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L15" s="1">
         <v>0</v>
@@ -2037,30 +2055,30 @@
     <row r="16" ht="15" customHeight="1" spans="1:16">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
-        <v>3002</v>
+        <v>2003</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E16" s="1">
-        <v>10102</v>
+        <v>10003</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G16" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" s="1">
-        <v>4</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1" t="s">
-        <v>67</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16" s="1"/>
       <c r="K16" s="1">
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="L16" s="1">
         <v>0</v>
@@ -2081,33 +2099,33 @@
     <row r="17" ht="15" customHeight="1" spans="1:16">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
-        <v>3003</v>
+        <v>2004</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E17" s="1">
-        <v>10103</v>
+        <v>10004</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G17" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" s="1">
-        <v>2</v>
-      </c>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1" t="s">
-        <v>70</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J17" s="1"/>
       <c r="K17" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="1">
         <v>1</v>
@@ -2125,30 +2143,30 @@
     <row r="18" ht="15" customHeight="1" spans="1:16">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
-        <v>4001</v>
+        <v>3001</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E18" s="1">
-        <v>10201</v>
+        <v>10101</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G18" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="1">
         <v>1</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L18" s="1">
         <v>0</v>
@@ -2169,32 +2187,30 @@
     <row r="19" ht="15" customHeight="1" spans="1:16">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
-        <v>4002</v>
+        <v>3002</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E19" s="1">
-        <v>10202</v>
+        <v>10102</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G19" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="1">
-        <v>5</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>55</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="I19" s="1"/>
       <c r="J19" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K19" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L19" s="1">
         <v>0</v>
@@ -2215,31 +2231,33 @@
     <row r="20" ht="15" customHeight="1" spans="1:16">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
-        <v>4003</v>
+        <v>3003</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E20" s="1">
-        <v>10203</v>
+        <v>10103</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
+      <c r="J20" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="K20" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="1">
         <v>1</v>
@@ -2257,30 +2275,30 @@
     <row r="21" ht="15" customHeight="1" spans="1:16">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
-        <v>5001</v>
+        <v>4001</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="1">
+        <v>10201</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="E21" s="1">
-        <v>15001</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1</v>
-      </c>
-      <c r="H21" s="1">
-        <v>3</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
@@ -2301,30 +2319,32 @@
     <row r="22" ht="15" customHeight="1" spans="1:16">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
-        <v>5003</v>
+        <v>4002</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="1">
+        <v>10202</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1">
+        <v>5</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E22" s="1">
-        <v>15003</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1</v>
-      </c>
-      <c r="H22" s="1">
-        <v>1</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J22" s="1"/>
       <c r="K22" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>
@@ -2345,30 +2365,28 @@
     <row r="23" ht="15" customHeight="1" spans="1:16">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
-        <v>5005</v>
+        <v>4003</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E23" s="1">
-        <v>15005</v>
+        <v>10203</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G23" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" s="1"/>
-      <c r="J23" s="1" t="s">
-        <v>67</v>
-      </c>
+      <c r="J23" s="1"/>
       <c r="K23" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L23" s="1">
         <v>0</v>
@@ -2389,30 +2407,30 @@
     <row r="24" ht="15" customHeight="1" spans="1:16">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
-        <v>5007</v>
+        <v>5001</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="1">
+        <v>15001</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1">
+        <v>3</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E24" s="1">
-        <v>15007</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G24" s="1">
-        <v>2</v>
-      </c>
-      <c r="H24" s="1">
-        <v>4</v>
-      </c>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1" t="s">
-        <v>89</v>
-      </c>
+      <c r="J24" s="1"/>
       <c r="K24" s="1">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="L24" s="1">
         <v>0</v>
@@ -2433,30 +2451,30 @@
     <row r="25" ht="15" customHeight="1" spans="1:16">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
-        <v>5008</v>
+        <v>5003</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="1">
+        <v>15003</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="E25" s="1">
-        <v>15008</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G25" s="1">
-        <v>1</v>
-      </c>
-      <c r="H25" s="1">
-        <v>1</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L25" s="1">
         <v>0</v>
@@ -2477,17 +2495,17 @@
     <row r="26" ht="15" customHeight="1" spans="1:16">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
-        <v>5009</v>
+        <v>5005</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E26" s="1">
-        <v>15009</v>
+        <v>15005</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G26" s="1">
         <v>2</v>
@@ -2497,10 +2515,10 @@
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="K26" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L26" s="1">
         <v>0</v>
@@ -2521,30 +2539,30 @@
     <row r="27" ht="15" customHeight="1" spans="1:16">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
-        <v>5011</v>
+        <v>5007</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E27" s="1">
-        <v>15011</v>
+        <v>15007</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G27" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="1">
-        <v>5</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="J27" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="K27" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L27" s="1">
         <v>0</v>
@@ -2565,17 +2583,17 @@
     <row r="28" ht="15" customHeight="1" spans="1:16">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
-        <v>5012</v>
+        <v>5008</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E28" s="1">
-        <v>15012</v>
+        <v>15008</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
@@ -2584,7 +2602,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1">
@@ -2609,33 +2627,33 @@
     <row r="29" ht="15" customHeight="1" spans="1:16">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
-        <v>5013</v>
+        <v>5009</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E29" s="1">
-        <v>15013</v>
+        <v>15009</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G29" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="1">
-        <v>2</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J29" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="K29" s="1">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L29" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M29" s="1">
         <v>1</v>
@@ -2653,30 +2671,30 @@
     <row r="30" ht="15" customHeight="1" spans="1:16">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
-        <v>5014</v>
+        <v>5011</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E30" s="1">
-        <v>15014</v>
+        <v>15011</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
       </c>
       <c r="H30" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L30" s="1">
         <v>0</v>
@@ -2697,30 +2715,30 @@
     <row r="31" ht="15" customHeight="1" spans="1:16">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
-        <v>5015</v>
+        <v>5012</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E31" s="1">
-        <v>15015</v>
+        <v>15012</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
       </c>
       <c r="H31" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L31" s="1">
         <v>0</v>
@@ -2741,33 +2759,33 @@
     <row r="32" ht="15" customHeight="1" spans="1:16">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
-        <v>5017</v>
+        <v>5013</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E32" s="1">
-        <v>15017</v>
+        <v>15013</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G32" s="1">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1">
         <v>2</v>
       </c>
-      <c r="H32" s="1">
-        <v>1</v>
-      </c>
       <c r="I32" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1">
         <v>15</v>
       </c>
       <c r="L32" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M32" s="1">
         <v>1</v>
@@ -2785,26 +2803,26 @@
     <row r="33" ht="15" customHeight="1" spans="1:16">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
-        <v>5018</v>
+        <v>5014</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E33" s="1">
-        <v>15018</v>
+        <v>15014</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G33" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="1">
         <v>1</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1">
@@ -2829,30 +2847,30 @@
     <row r="34" ht="15" customHeight="1" spans="1:16">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
-        <v>5019</v>
+        <v>5015</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E34" s="1">
-        <v>15019</v>
+        <v>15015</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G34" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" s="1">
-        <v>4</v>
-      </c>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1" t="s">
-        <v>119</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J34" s="1"/>
       <c r="K34" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L34" s="1">
         <v>0</v>
@@ -2873,30 +2891,30 @@
     <row r="35" ht="15" customHeight="1" spans="1:16">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
-        <v>5020</v>
+        <v>5017</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E35" s="1">
-        <v>15020</v>
+        <v>15017</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G35" s="1">
         <v>2</v>
       </c>
       <c r="H35" s="1">
-        <v>4</v>
-      </c>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1" t="s">
-        <v>122</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J35" s="1"/>
       <c r="K35" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
@@ -2917,33 +2935,33 @@
     <row r="36" ht="15" customHeight="1" spans="1:16">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
-        <v>5021</v>
+        <v>5018</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E36" s="1">
-        <v>15021</v>
+        <v>15018</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G36" s="1">
         <v>2</v>
       </c>
       <c r="H36" s="1">
-        <v>2</v>
-      </c>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1" t="s">
-        <v>125</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J36" s="1"/>
       <c r="K36" s="1">
         <v>15</v>
       </c>
       <c r="L36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="1">
         <v>1</v>
@@ -2960,39 +2978,135 @@
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:16">
       <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
+      <c r="B37" s="1">
+        <v>5019</v>
+      </c>
       <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+      <c r="D37" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E37" s="1">
+        <v>15019</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G37" s="1">
+        <v>2</v>
+      </c>
+      <c r="H37" s="1">
+        <v>4</v>
+      </c>
       <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
+      <c r="J37" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K37" s="1">
+        <v>10</v>
+      </c>
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <v>1</v>
+      </c>
+      <c r="N37" s="1">
+        <v>0</v>
+      </c>
+      <c r="O37" s="1">
+        <v>0</v>
+      </c>
+      <c r="P37" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:16">
       <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
+      <c r="B38" s="1">
+        <v>5020</v>
+      </c>
       <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
+      <c r="D38" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38" s="1">
+        <v>15020</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G38" s="1">
+        <v>2</v>
+      </c>
+      <c r="H38" s="1">
+        <v>4</v>
+      </c>
       <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
+      <c r="J38" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K38" s="1">
+        <v>10</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <v>1</v>
+      </c>
+      <c r="N38" s="1">
+        <v>0</v>
+      </c>
+      <c r="O38" s="1">
+        <v>0</v>
+      </c>
+      <c r="P38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" spans="1:16">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1">
+        <v>5021</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E39" s="1">
+        <v>15021</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G39" s="1">
+        <v>2</v>
+      </c>
+      <c r="H39" s="1">
+        <v>2</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K39" s="1">
+        <v>15</v>
+      </c>
+      <c r="L39" s="1">
+        <v>1</v>
+      </c>
+      <c r="M39" s="1">
+        <v>1</v>
+      </c>
+      <c r="N39" s="1">
+        <v>0</v>
+      </c>
+      <c r="O39" s="1">
+        <v>0</v>
+      </c>
+      <c r="P39" s="1">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AAAGameData/DataTables/BuffTable.xlsx
+++ b/AAAGameData/DataTables/BuffTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="152">
   <si>
     <t>#</t>
   </si>
@@ -47,6 +47,9 @@
     <t>Desc</t>
   </si>
   <si>
+    <t>IsHidden</t>
+  </si>
+  <si>
     <t>BuffType</t>
   </si>
   <si>
@@ -99,6 +102,9 @@
   </si>
   <si>
     <t>Buff描述</t>
+  </si>
+  <si>
+    <t>是否隐藏图标（羁绊相关Buff隐藏）</t>
   </si>
   <si>
     <t>Buff类型：- 1 : 增益 (Buff)- 2 : 减益 (Debuff)</t>
@@ -1448,7 +1454,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1457,15 +1463,16 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="50" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="12" width="50" customWidth="1"/>
-    <col min="13" max="13" width="44" customWidth="1"/>
-    <col min="14" max="14" width="42" customWidth="1"/>
-    <col min="15" max="15" width="50" customWidth="1"/>
-    <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="7" max="7" width="8.625" customWidth="1"/>
+    <col min="8" max="8" width="48" customWidth="1"/>
+    <col min="9" max="13" width="50" customWidth="1"/>
+    <col min="14" max="14" width="44" customWidth="1"/>
+    <col min="15" max="15" width="42" customWidth="1"/>
+    <col min="16" max="16" width="50" customWidth="1"/>
+    <col min="17" max="17" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1486,8 +1493,9 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1534,183 +1542,195 @@
       <c r="P2" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="H3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" ht="54" spans="1:16">
+        <v>17</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="67.5" spans="1:17">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:16">
+        <v>34</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:17">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" s="1">
         <v>1401</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1">
         <v>2</v>
       </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="1">
+      <c r="I5" s="1">
+        <v>2</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="1">
         <v>10</v>
       </c>
-      <c r="L5" s="1">
-        <v>1</v>
-      </c>
       <c r="M5" s="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1">
         <v>10</v>
       </c>
-      <c r="N5" s="1">
-        <v>0</v>
-      </c>
       <c r="O5" s="1">
         <v>0</v>
       </c>
       <c r="P5" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="1:16">
+      <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:17">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E6" s="1">
         <v>1402</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
         <v>2</v>
       </c>
-      <c r="H6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
       <c r="J6" s="1"/>
-      <c r="K6" s="1">
+      <c r="K6" s="1"/>
+      <c r="L6" s="1">
         <v>10</v>
       </c>
-      <c r="L6" s="1">
-        <v>0</v>
-      </c>
       <c r="M6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -1718,41 +1738,44 @@
       <c r="P6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:16">
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:17">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" s="1">
         <v>1403</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
         <v>2</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>5</v>
       </c>
-      <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="1">
         <v>0</v>
       </c>
       <c r="M7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -1760,43 +1783,46 @@
       <c r="P7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:16">
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:17">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E8" s="1">
         <v>1404</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1">
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1">
         <v>8</v>
       </c>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
       <c r="M8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="1">
         <v>0</v>
@@ -1804,43 +1830,46 @@
       <c r="P8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:16">
+      <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:17">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E9" s="1">
         <v>1405</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
         <v>1</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K9" s="1"/>
       <c r="L9" s="1">
         <v>0</v>
       </c>
       <c r="M9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -1848,43 +1877,46 @@
       <c r="P9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="1:16">
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:17">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>6</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E10" s="1">
         <v>1406</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
         <v>2</v>
       </c>
-      <c r="H10" s="1">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1">
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1">
         <v>4</v>
       </c>
-      <c r="L10" s="1">
-        <v>0</v>
-      </c>
       <c r="M10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -1892,83 +1924,89 @@
       <c r="P10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" spans="1:16">
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:17">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>7</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E11" s="1">
         <v>1407</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
         <v>2</v>
       </c>
-      <c r="H11" s="1">
-        <v>1</v>
-      </c>
-      <c r="I11" s="1"/>
+      <c r="I11" s="1">
+        <v>1</v>
+      </c>
       <c r="J11" s="1"/>
-      <c r="K11" s="1">
+      <c r="K11" s="1"/>
+      <c r="L11" s="1">
         <v>6</v>
       </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
       <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
         <v>2</v>
       </c>
-      <c r="N11" s="1">
-        <v>0</v>
-      </c>
       <c r="O11" s="1">
         <v>0</v>
       </c>
       <c r="P11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="1:16">
+      <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:17">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>8</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E12" s="1">
         <v>1408</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
       </c>
-      <c r="I12" s="1"/>
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
       <c r="J12" s="1"/>
-      <c r="K12" s="1">
+      <c r="K12" s="1"/>
+      <c r="L12" s="1">
         <v>5</v>
       </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
       <c r="M12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="1">
         <v>0</v>
@@ -1976,41 +2014,44 @@
       <c r="P12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" spans="1:16">
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:17">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>9</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E13" s="1">
         <v>1409</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
         <v>2</v>
       </c>
-      <c r="H13" s="1">
-        <v>1</v>
-      </c>
-      <c r="I13" s="1"/>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
       <c r="J13" s="1"/>
-      <c r="K13" s="1">
+      <c r="K13" s="1"/>
+      <c r="L13" s="1">
         <v>2</v>
       </c>
-      <c r="L13" s="1">
-        <v>0</v>
-      </c>
       <c r="M13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="1">
         <v>0</v>
@@ -2018,43 +2059,46 @@
       <c r="P13" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" spans="1:16">
+      <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:17">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>10</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E14" s="1">
         <v>1410</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1">
         <v>5</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
+      <c r="J14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K14" s="1"/>
       <c r="L14" s="1">
         <v>0</v>
       </c>
       <c r="M14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="1">
         <v>0</v>
@@ -2062,41 +2106,44 @@
       <c r="P14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" spans="1:16">
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:17">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>21</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E15" s="1">
         <v>1407</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1">
         <v>5</v>
       </c>
-      <c r="I15" s="1"/>
       <c r="J15" s="1"/>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
+      <c r="K15" s="1"/>
       <c r="L15" s="1">
         <v>0</v>
       </c>
       <c r="M15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="1">
         <v>0</v>
@@ -2104,43 +2151,46 @@
       <c r="P15" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" spans="1:16">
+      <c r="Q15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:17">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>22</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E16" s="1">
         <v>10002</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
       </c>
-      <c r="I16" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
+      <c r="I16" s="1">
+        <v>1</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K16" s="1"/>
       <c r="L16" s="1">
         <v>0</v>
       </c>
       <c r="M16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
@@ -2148,43 +2198,46 @@
       <c r="P16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" spans="1:16">
+      <c r="Q16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:17">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>23</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E17" s="1">
         <v>10001</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G17" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1">
         <v>2</v>
       </c>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="K17" s="1">
+      <c r="I17" s="1">
+        <v>2</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L17" s="1">
         <v>4</v>
       </c>
-      <c r="L17" s="1">
+      <c r="M17" s="1">
         <v>0.5</v>
       </c>
-      <c r="M17" s="1">
-        <v>1</v>
-      </c>
       <c r="N17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="1">
         <v>0</v>
@@ -2192,43 +2245,46 @@
       <c r="P17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" spans="1:16">
+      <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:17">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>24</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E18" s="1">
         <v>15008</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" s="1">
         <v>1</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1">
-        <v>0</v>
-      </c>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K18" s="1"/>
       <c r="L18" s="1">
         <v>0</v>
       </c>
       <c r="M18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" s="1">
         <v>0</v>
@@ -2236,43 +2292,46 @@
       <c r="P18" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" spans="1:16">
+      <c r="Q18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:17">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>25</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E19" s="1">
         <v>15015</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1">
         <v>5</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1">
-        <v>0</v>
-      </c>
+      <c r="J19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K19" s="1"/>
       <c r="L19" s="1">
         <v>0</v>
       </c>
       <c r="M19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="1">
         <v>0</v>
@@ -2280,43 +2339,46 @@
       <c r="P19" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" spans="1:16">
+      <c r="Q19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:17">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>28</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E20" s="1">
         <v>1411</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1">
-        <v>0</v>
-      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K20" s="1"/>
       <c r="L20" s="1">
         <v>0</v>
       </c>
       <c r="M20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" s="1">
         <v>0</v>
@@ -2324,43 +2386,46 @@
       <c r="P20" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" spans="1:16">
+      <c r="Q20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:17">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>2001</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E21" s="1">
         <v>10001</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
         <v>1</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1">
+      <c r="I21" s="1">
+        <v>1</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1">
         <v>8</v>
       </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
       <c r="M21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="1">
         <v>0</v>
@@ -2368,43 +2433,46 @@
       <c r="P21" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" spans="1:16">
+      <c r="Q21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:17">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>2002</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E22" s="1">
         <v>10002</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="1">
         <v>1</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1">
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1">
         <v>10</v>
       </c>
-      <c r="L22" s="1">
-        <v>0</v>
-      </c>
       <c r="M22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -2412,43 +2480,46 @@
       <c r="P22" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" spans="1:16">
+      <c r="Q22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="1:17">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>2003</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E23" s="1">
         <v>10003</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="1">
         <v>1</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1">
+      <c r="I23" s="1">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1">
         <v>8</v>
       </c>
-      <c r="L23" s="1">
-        <v>0</v>
-      </c>
       <c r="M23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" s="1">
         <v>0</v>
@@ -2456,43 +2527,46 @@
       <c r="P23" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" spans="1:16">
+      <c r="Q23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:17">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>2004</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E24" s="1">
         <v>10004</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="1">
         <v>1</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1">
+      <c r="I24" s="1">
+        <v>1</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1">
         <v>10</v>
       </c>
-      <c r="L24" s="1">
-        <v>0</v>
-      </c>
       <c r="M24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" s="1">
         <v>0</v>
@@ -2500,43 +2574,46 @@
       <c r="P24" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" spans="1:16">
+      <c r="Q24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:17">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>3001</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E25" s="1">
         <v>10101</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
         <v>2</v>
       </c>
-      <c r="H25" s="1">
-        <v>1</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1">
+      <c r="I25" s="1">
+        <v>1</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1">
         <v>2</v>
       </c>
-      <c r="L25" s="1">
-        <v>0</v>
-      </c>
       <c r="M25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" s="1">
         <v>0</v>
@@ -2544,43 +2621,46 @@
       <c r="P25" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" spans="1:16">
+      <c r="Q25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:17">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>3002</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E26" s="1">
         <v>10102</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
         <v>2</v>
       </c>
-      <c r="H26" s="1">
+      <c r="I26" s="1">
         <v>4</v>
       </c>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="K26" s="1">
+      <c r="J26" s="1"/>
+      <c r="K26" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L26" s="1">
         <v>0.8</v>
       </c>
-      <c r="L26" s="1">
-        <v>0</v>
-      </c>
       <c r="M26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" s="1">
         <v>0</v>
@@ -2588,43 +2668,46 @@
       <c r="P26" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" spans="1:16">
+      <c r="Q26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:17">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>3003</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E27" s="1">
         <v>10103</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G27" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" s="1">
         <v>2</v>
       </c>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="K27" s="1">
+      <c r="I27" s="1">
+        <v>2</v>
+      </c>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L27" s="1">
         <v>6</v>
       </c>
-      <c r="L27" s="1">
-        <v>1</v>
-      </c>
       <c r="M27" s="1">
         <v>1</v>
       </c>
       <c r="N27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="1">
         <v>0</v>
@@ -2632,43 +2715,46 @@
       <c r="P27" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" spans="1:16">
+      <c r="Q27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="1:17">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>4001</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E28" s="1">
         <v>10201</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="1">
         <v>1</v>
       </c>
-      <c r="I28" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1">
+      <c r="I28" s="1">
+        <v>1</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1">
         <v>10</v>
       </c>
-      <c r="L28" s="1">
-        <v>0</v>
-      </c>
       <c r="M28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" s="1">
         <v>0</v>
@@ -2676,45 +2762,48 @@
       <c r="P28" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" spans="1:16">
+      <c r="Q28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="1:17">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>4002</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E29" s="1">
         <v>10202</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="1">
+        <v>1</v>
+      </c>
+      <c r="I29" s="1">
         <v>5</v>
       </c>
-      <c r="I29" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="J29" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="K29" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="L29" s="1">
         <v>0</v>
       </c>
       <c r="M29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="1">
         <v>0</v>
@@ -2722,41 +2811,44 @@
       <c r="P29" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" spans="1:16">
+      <c r="Q29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" spans="1:17">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>4003</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E30" s="1">
         <v>10203</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" s="1">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1">
         <v>5</v>
       </c>
-      <c r="I30" s="1"/>
       <c r="J30" s="1"/>
-      <c r="K30" s="1">
-        <v>0</v>
-      </c>
+      <c r="K30" s="1"/>
       <c r="L30" s="1">
         <v>0</v>
       </c>
       <c r="M30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="1">
         <v>0</v>
@@ -2764,43 +2856,46 @@
       <c r="P30" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" spans="1:16">
+      <c r="Q30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" spans="1:17">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
         <v>5001</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E31" s="1">
         <v>15001</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="1">
+        <v>1</v>
+      </c>
+      <c r="I31" s="1">
         <v>3</v>
       </c>
-      <c r="I31" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1">
+      <c r="J31" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1">
         <v>30</v>
       </c>
-      <c r="L31" s="1">
-        <v>0</v>
-      </c>
       <c r="M31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
@@ -2808,43 +2903,46 @@
       <c r="P31" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" spans="1:16">
+      <c r="Q31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" spans="1:17">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
         <v>5003</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E32" s="1">
         <v>15003</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="1">
         <v>1</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1">
+      <c r="I32" s="1">
+        <v>1</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1">
         <v>8</v>
       </c>
-      <c r="L32" s="1">
-        <v>0</v>
-      </c>
       <c r="M32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" s="1">
         <v>0</v>
@@ -2852,43 +2950,46 @@
       <c r="P32" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" spans="1:16">
+      <c r="Q32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" spans="1:17">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
         <v>5005</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E33" s="1">
         <v>15005</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
         <v>2</v>
       </c>
-      <c r="H33" s="1">
+      <c r="I33" s="1">
         <v>4</v>
       </c>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="K33" s="1">
+      <c r="J33" s="1"/>
+      <c r="K33" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L33" s="1">
         <v>2</v>
       </c>
-      <c r="L33" s="1">
-        <v>0</v>
-      </c>
       <c r="M33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" s="1">
         <v>0</v>
@@ -2896,43 +2997,46 @@
       <c r="P33" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" spans="1:16">
+      <c r="Q33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" spans="1:17">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
         <v>5007</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E34" s="1">
         <v>15007</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
         <v>2</v>
       </c>
-      <c r="H34" s="1">
+      <c r="I34" s="1">
         <v>4</v>
       </c>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="K34" s="1">
+      <c r="J34" s="1"/>
+      <c r="K34" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="L34" s="1">
         <v>3</v>
       </c>
-      <c r="L34" s="1">
-        <v>0</v>
-      </c>
       <c r="M34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -2940,43 +3044,46 @@
       <c r="P34" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" spans="1:16">
+      <c r="Q34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" spans="1:17">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
         <v>5008</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E35" s="1">
         <v>15008</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="1">
         <v>1</v>
       </c>
-      <c r="I35" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1">
+      <c r="I35" s="1">
+        <v>1</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1">
         <v>10</v>
       </c>
-      <c r="L35" s="1">
-        <v>0</v>
-      </c>
       <c r="M35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="1">
         <v>0</v>
@@ -2984,43 +3091,46 @@
       <c r="P35" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" spans="1:16">
+      <c r="Q35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" spans="1:17">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
         <v>5009</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E36" s="1">
         <v>15009</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
         <v>2</v>
       </c>
-      <c r="H36" s="1">
+      <c r="I36" s="1">
         <v>4</v>
       </c>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="K36" s="1">
+      <c r="J36" s="1"/>
+      <c r="K36" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L36" s="1">
         <v>4</v>
       </c>
-      <c r="L36" s="1">
-        <v>0</v>
-      </c>
       <c r="M36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" s="1">
         <v>0</v>
@@ -3028,43 +3138,46 @@
       <c r="P36" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" spans="1:16">
+      <c r="Q36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" spans="1:17">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
         <v>5011</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E37" s="1">
         <v>15011</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="1">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1">
         <v>5</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1">
+      <c r="J37" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1">
         <v>10</v>
       </c>
-      <c r="L37" s="1">
-        <v>0</v>
-      </c>
       <c r="M37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -3072,43 +3185,46 @@
       <c r="P37" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" spans="1:16">
+      <c r="Q37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" spans="1:17">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
         <v>5012</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E38" s="1">
         <v>15012</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="1">
         <v>1</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1">
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1">
         <v>10</v>
       </c>
-      <c r="L38" s="1">
-        <v>0</v>
-      </c>
       <c r="M38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" s="1">
         <v>0</v>
@@ -3116,43 +3232,46 @@
       <c r="P38" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" spans="1:16">
+      <c r="Q38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" spans="1:17">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
         <v>5013</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E39" s="1">
         <v>15013</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="1">
+        <v>1</v>
+      </c>
+      <c r="I39" s="1">
         <v>2</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1">
+      <c r="J39" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1">
         <v>15</v>
       </c>
-      <c r="L39" s="1">
+      <c r="M39" s="1">
         <v>3</v>
       </c>
-      <c r="M39" s="1">
-        <v>1</v>
-      </c>
       <c r="N39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" s="1">
         <v>0</v>
@@ -3160,43 +3279,46 @@
       <c r="P39" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" spans="1:16">
+      <c r="Q39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" spans="1:17">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
         <v>5014</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E40" s="1">
         <v>15014</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1">
         <v>1</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1">
+      <c r="I40" s="1">
+        <v>1</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1">
         <v>15</v>
       </c>
-      <c r="L40" s="1">
-        <v>0</v>
-      </c>
       <c r="M40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" s="1">
         <v>0</v>
@@ -3204,43 +3326,46 @@
       <c r="P40" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" spans="1:16">
+      <c r="Q40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" spans="1:17">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
         <v>5015</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E41" s="1">
         <v>15015</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="1">
+        <v>1</v>
+      </c>
+      <c r="I41" s="1">
         <v>5</v>
       </c>
-      <c r="I41" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1">
-        <v>0</v>
-      </c>
+      <c r="J41" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K41" s="1"/>
       <c r="L41" s="1">
         <v>0</v>
       </c>
       <c r="M41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" s="1">
         <v>0</v>
@@ -3248,43 +3373,46 @@
       <c r="P41" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" spans="1:16">
+      <c r="Q41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" spans="1:17">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
         <v>5017</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E42" s="1">
         <v>15017</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
         <v>2</v>
       </c>
-      <c r="H42" s="1">
-        <v>1</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1">
+      <c r="I42" s="1">
+        <v>1</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1">
         <v>15</v>
       </c>
-      <c r="L42" s="1">
-        <v>0</v>
-      </c>
       <c r="M42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -3292,43 +3420,46 @@
       <c r="P42" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" spans="1:16">
+      <c r="Q42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" spans="1:17">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
         <v>5018</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E43" s="1">
         <v>15018</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
         <v>2</v>
       </c>
-      <c r="H43" s="1">
-        <v>1</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1">
+      <c r="I43" s="1">
+        <v>1</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1">
         <v>15</v>
       </c>
-      <c r="L43" s="1">
-        <v>0</v>
-      </c>
       <c r="M43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" s="1">
         <v>0</v>
@@ -3336,43 +3467,46 @@
       <c r="P43" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" spans="1:16">
+      <c r="Q43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" spans="1:17">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
         <v>5019</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E44" s="1">
         <v>15019</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
         <v>2</v>
       </c>
-      <c r="H44" s="1">
+      <c r="I44" s="1">
         <v>4</v>
       </c>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="K44" s="1">
+      <c r="J44" s="1"/>
+      <c r="K44" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L44" s="1">
         <v>10</v>
       </c>
-      <c r="L44" s="1">
-        <v>0</v>
-      </c>
       <c r="M44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" s="1">
         <v>0</v>
@@ -3380,43 +3514,46 @@
       <c r="P44" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" spans="1:16">
+      <c r="Q44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" spans="1:17">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
         <v>5020</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E45" s="1">
         <v>15020</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
         <v>2</v>
       </c>
-      <c r="H45" s="1">
+      <c r="I45" s="1">
         <v>4</v>
       </c>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="K45" s="1">
+      <c r="J45" s="1"/>
+      <c r="K45" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L45" s="1">
         <v>10</v>
       </c>
-      <c r="L45" s="1">
-        <v>0</v>
-      </c>
       <c r="M45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -3424,43 +3561,46 @@
       <c r="P45" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" spans="1:16">
+      <c r="Q45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" spans="1:17">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
         <v>5021</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E46" s="1">
         <v>15021</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G46" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H46" s="1">
         <v>2</v>
       </c>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="K46" s="1">
+      <c r="I46" s="1">
+        <v>2</v>
+      </c>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="L46" s="1">
         <v>15</v>
       </c>
-      <c r="L46" s="1">
-        <v>1</v>
-      </c>
       <c r="M46" s="1">
         <v>1</v>
       </c>
       <c r="N46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" s="1">
         <v>0</v>
@@ -3468,9 +3608,12 @@
       <c r="P46" s="1">
         <v>0</v>
       </c>
+      <c r="Q46" s="1">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <sortState ref="B5:P46">
+  <sortState ref="B5:Q46">
     <sortCondition ref="B5:B46"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AAAGameData/DataTables/BuffTable.xlsx
+++ b/AAAGameData/DataTables/BuffTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="220">
   <si>
     <t>#</t>
   </si>
@@ -47,6 +47,9 @@
     <t>Desc</t>
   </si>
   <si>
+    <t>StoryDesc</t>
+  </si>
+  <si>
     <t>IsHidden</t>
   </si>
   <si>
@@ -104,6 +107,9 @@
     <t>Buff描述</t>
   </si>
   <si>
+    <t>故事文本描述</t>
+  </si>
+  <si>
     <t>是否隐藏图标（羁绊相关Buff隐藏）</t>
   </si>
   <si>
@@ -143,6 +149,9 @@
     <t>每秒每层造成5点伤害，5/10层减50物抗</t>
   </si>
   <si>
+    <t>焰色层叠，甲破魂消，灼尽一切。</t>
+  </si>
+  <si>
     <t>{"DamagePerStack":5}</t>
   </si>
   <si>
@@ -152,18 +161,27 @@
     <t>降低15%移速和5%攻速，遇灼烧触发融化</t>
   </si>
   <si>
+    <t>寒意从脚底蔓延，每一步都像踩在泥泞里。</t>
+  </si>
+  <si>
     <t>融化</t>
   </si>
   <si>
     <t>30%法强×灼烧层数的真实伤害</t>
   </si>
   <si>
+    <t>冰与火的相遇，会碰撞出什么样的结局呢？</t>
+  </si>
+  <si>
     <t>神力增益</t>
   </si>
   <si>
     <t>攻击力+25%，攻击附带灼烧效果</t>
   </si>
   <si>
+    <t>神威附体，攻势如焰，灼烧随行。</t>
+  </si>
+  <si>
     <t>{"AtkDamage":"25%"}</t>
   </si>
   <si>
@@ -173,6 +191,9 @@
     <t>白天伤害+15%射程+30%</t>
   </si>
   <si>
+    <t>日落之前，没有人能逃出他的射程。</t>
+  </si>
+  <si>
     <t>{"AtkDamage":"15%","AtkRange":"30%"}</t>
   </si>
   <si>
@@ -182,6 +203,9 @@
     <t>降低30%移速和15%攻速</t>
   </si>
   <si>
+    <t>寒意入骨，手脚俱僵。</t>
+  </si>
+  <si>
     <t>{"MoveSpeed":"-30%","AtkSpeed":"-15%"}</t>
   </si>
   <si>
@@ -191,24 +215,36 @@
     <t>每层降低5%护甲和魔抗，持续6s，最多10层</t>
   </si>
   <si>
+    <t>黑暗的侵蚀无声无息。</t>
+  </si>
+  <si>
     <t>黑暗狂暴</t>
   </si>
   <si>
     <t>攻速+30%，持续5s</t>
   </si>
   <si>
+    <t>黑暗狂涌，迅如疾风！</t>
+  </si>
+  <si>
     <t>恐惧</t>
   </si>
   <si>
     <t>攻击力-20%，持续2s</t>
   </si>
   <si>
+    <t>恐惧是最好的枷锁，它让人忘记自己其实有多么强大。</t>
+  </si>
+  <si>
     <t>虚无之躯</t>
   </si>
   <si>
     <t>物理伤害减免30%</t>
   </si>
   <si>
+    <t>你的剑穿过了他，却什么都没有伤到。</t>
+  </si>
+  <si>
     <t>{"PhysicalDamageReduce":"30%"}</t>
   </si>
   <si>
@@ -218,12 +254,18 @@
     <t>所有攻击附带腐蚀效果</t>
   </si>
   <si>
+    <t>那曾经照耀苍生的神力，如今已被黑暗彻底侵染。</t>
+  </si>
+  <si>
     <t>黑暗杨戬·阶段二</t>
   </si>
   <si>
     <t>攻击力+30%，移动速度+20%</t>
   </si>
   <si>
+    <t>他变得更快，也更危险了。</t>
+  </si>
+  <si>
     <t>{"AtkDamage":"30%","MoveSpeed":"20%"}</t>
   </si>
   <si>
@@ -233,6 +275,9 @@
     <t>每0.5s扣除1%最大生命值，持续4s</t>
   </si>
   <si>
+    <t>伤口不肯愈合，每时每刻都在提醒你，你正在失去什么。</t>
+  </si>
+  <si>
     <t>{"DamageRatio":0.01}</t>
   </si>
   <si>
@@ -242,6 +287,9 @@
     <t>攻击力+60%，护甲-50%，暴击率+40%，免疫控制</t>
   </si>
   <si>
+    <t>甲碎魂决，攻势如狂，死志已决，与尔俱亡。</t>
+  </si>
+  <si>
     <t>{"AtkDamage":"60%","Armor":"-50%","CritRate":"40%"}</t>
   </si>
   <si>
@@ -251,12 +299,18 @@
     <t>普攻和技能附带30%吸血效果</t>
   </si>
   <si>
+    <t>猜猜我的身体里还有多少血是自己的？</t>
+  </si>
+  <si>
     <t>{"lifestealRatio":0.3}</t>
   </si>
   <si>
     <t>夜晚法强+20%</t>
   </si>
   <si>
+    <t>夜幕降临，玄冰的力量随月光一同涌现。</t>
+  </si>
+  <si>
     <t>{"SpellPower":"20%"}</t>
   </si>
   <si>
@@ -266,6 +320,9 @@
     <t>移动速度提升20%，持续8秒</t>
   </si>
   <si>
+    <t>先发制人，克敌制胜！</t>
+  </si>
+  <si>
     <t>{"MoveSpeed":"20%"}</t>
   </si>
   <si>
@@ -275,6 +332,9 @@
     <t>攻击力提升15%，持续10秒</t>
   </si>
   <si>
+    <t>攻势如潮，先声夺人！</t>
+  </si>
+  <si>
     <t>{"AtkDamage":"15%"}</t>
   </si>
   <si>
@@ -284,6 +344,9 @@
     <t>首8秒内受伤减少50%</t>
   </si>
   <si>
+    <t>抢先布防，立于不败！</t>
+  </si>
+  <si>
     <t>{"DamageTakenMultiplier":"-50%"}</t>
   </si>
   <si>
@@ -293,6 +356,9 @@
     <t>防御力提升20%，持续10秒</t>
   </si>
   <si>
+    <t>先手固防，稳如泰山！</t>
+  </si>
+  <si>
     <t>{"Armor":"20%"}</t>
   </si>
   <si>
@@ -302,6 +368,9 @@
     <t>敌人防御降低30%，持续2秒内所有攻击伤害+40%</t>
   </si>
   <si>
+    <t>出其不意，攻其不备！</t>
+  </si>
+  <si>
     <t>{"Armor":"-30%","DamageTakenMultiplier":"40%"}</t>
   </si>
   <si>
@@ -311,6 +380,9 @@
     <t>敌人眩晕0.8秒，无法行动</t>
   </si>
   <si>
+    <t>出手无声，一击制敌！</t>
+  </si>
+  <si>
     <t>{"SpecialState":"Stun"}</t>
   </si>
   <si>
@@ -320,6 +392,9 @@
     <t>敌人持续流血6秒，每秒损失10%最大生命值</t>
   </si>
   <si>
+    <t>刀锋留痕，血尽命绝！</t>
+  </si>
+  <si>
     <t>{"DamageRatio":0.1}</t>
   </si>
   <si>
@@ -329,6 +404,9 @@
     <t>攻击速度提升20%，伤害提升15%，持续10秒</t>
   </si>
   <si>
+    <t>战意激昂，势不可挡！</t>
+  </si>
+  <si>
     <t>{"AtkSpeed":"20%","AtkDamage":"15%"}</t>
   </si>
   <si>
@@ -338,6 +416,9 @@
     <t>全体友方伤害提升15%；召唤师自身伤害提升30%（战场有友方HP低于50%时持续生效）</t>
   </si>
   <si>
+    <t>同伴们的鲜血激起了所有人的怒火。</t>
+  </si>
+  <si>
     <t>{"SummonerAtkDamage":"30%"}</t>
   </si>
   <si>
@@ -353,6 +434,9 @@
     <t>提供1000点护盾，持续30秒</t>
   </si>
   <si>
+    <t>神明的庇护凝聚成盾，能够抵挡一切伤害。</t>
+  </si>
+  <si>
     <t>{"Shield":1000}</t>
   </si>
   <si>
@@ -362,18 +446,27 @@
     <t>攻击力提升30%，移动速度提升20%，持续8秒</t>
   </si>
   <si>
+    <t>号角声响士气昂，千军辟易避锋芒。</t>
+  </si>
+  <si>
     <t>暗影突袭·眩晕</t>
   </si>
   <si>
     <t>眩晕2秒，无法行动</t>
   </si>
   <si>
-    <t>冰霜新星</t>
+    <t>暗影从背后袭来，在一睁眼已是永恒。</t>
+  </si>
+  <si>
+    <t>冰霜冲击</t>
   </si>
   <si>
     <t>冰冻3秒，无法行动</t>
   </si>
   <si>
+    <t>寒霜入骨，冻如顽石！</t>
+  </si>
+  <si>
     <t>{"SpecialState":"Freeze"}</t>
   </si>
   <si>
@@ -383,6 +476,9 @@
     <t>攻击力提升80%，防御降低30%，持续10秒</t>
   </si>
   <si>
+    <t>“求求你阻止我！”</t>
+  </si>
+  <si>
     <t>{"AtkDamage":"80%","Armor":"-30%"}</t>
   </si>
   <si>
@@ -392,6 +488,9 @@
     <t>陷入混乱4秒，有概率攻击队友</t>
   </si>
   <si>
+    <t>谁是敌人，谁是战友？</t>
+  </si>
+  <si>
     <t>{"SpecialState":"Confused"}</t>
   </si>
   <si>
@@ -401,6 +500,9 @@
     <t>返回受到伤害的30%，持续10秒</t>
   </si>
   <si>
+    <t>反弹~</t>
+  </si>
+  <si>
     <t>{"reflectDamageRatio":0.3}</t>
   </si>
   <si>
@@ -410,6 +512,9 @@
     <t>护甲提升30%，持续10秒</t>
   </si>
   <si>
+    <t>这将会是你们的叹息之墙。</t>
+  </si>
+  <si>
     <t>{"Armor":"30%"}</t>
   </si>
   <si>
@@ -419,6 +524,9 @@
     <t>每3秒恢复50点护盾，持续15秒</t>
   </si>
   <si>
+    <t>护盾会随着时间恢复。</t>
+  </si>
+  <si>
     <t>{"ShieldRegenPerSecond":50}</t>
   </si>
   <si>
@@ -428,6 +536,9 @@
     <t>最大生命值提升30%，持续15秒</t>
   </si>
   <si>
+    <t>古老的血脉在体内奔涌，似乎让他变得更加强大了。</t>
+  </si>
+  <si>
     <t>{"MaxHP":"30%"}</t>
   </si>
   <si>
@@ -437,6 +548,9 @@
     <t>对敌方造成伤害时吸血40%</t>
   </si>
   <si>
+    <t>以尔之鲜血，养吾之身躯。</t>
+  </si>
+  <si>
     <t>{"lifestealRatio":0.4}</t>
   </si>
   <si>
@@ -446,6 +560,9 @@
     <t>护甲降低5点，持续15秒</t>
   </si>
   <si>
+    <t>甲碎防线溃，敌刃势如摧。</t>
+  </si>
+  <si>
     <t>{"Armor":"-5"}</t>
   </si>
   <si>
@@ -455,6 +572,9 @@
     <t>攻击力降低30%，持续15秒</t>
   </si>
   <si>
+    <t>你的力量。。。将会像沙子一样流走。</t>
+  </si>
+  <si>
     <t>{"AtkDamage":"-30%"}</t>
   </si>
   <si>
@@ -464,6 +584,9 @@
     <t>禁用技能，持续10秒</t>
   </si>
   <si>
+    <t>你的技艺受到了封印，只能使用本能进行战斗。</t>
+  </si>
+  <si>
     <t>{"SpecialState":"Silence"}</t>
   </si>
   <si>
@@ -473,6 +596,9 @@
     <t>强制攻击目标，持续10秒</t>
   </si>
   <si>
+    <t>“哈哈哈哈哈哈哈哈哈”</t>
+  </si>
+  <si>
     <t>{"SpecialState":"Taunt"}</t>
   </si>
   <si>
@@ -480,6 +606,9 @@
   </si>
   <si>
     <t>每秒损失5%最大生命值，持续15秒</t>
+  </si>
+  <si>
+    <t>毒雾弥漫，每一秒都在侵蚀你的生命</t>
   </si>
   <si>
     <t>{"DamageRatio":0.05}</t>
@@ -570,14 +699,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1033,148 +1155,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1529,25 +1651,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:R55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="50" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
-    <col min="8" max="8" width="48" customWidth="1"/>
-    <col min="9" max="13" width="50" customWidth="1"/>
-    <col min="14" max="14" width="44" customWidth="1"/>
-    <col min="15" max="15" width="42" customWidth="1"/>
-    <col min="16" max="16" width="50" customWidth="1"/>
-    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="6" max="6" width="75.7777777777778" customWidth="1"/>
+    <col min="7" max="7" width="50.7777777777778" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="9" max="9" width="48" customWidth="1"/>
+    <col min="10" max="14" width="50" customWidth="1"/>
+    <col min="15" max="15" width="44" customWidth="1"/>
+    <col min="16" max="16" width="42" customWidth="1"/>
+    <col min="17" max="17" width="50" customWidth="1"/>
+    <col min="18" max="18" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1569,8 +1692,9 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" s="1"/>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1620,195 +1744,207 @@
       <c r="Q2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="54" spans="1:17">
+        <v>18</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" ht="57.6" spans="1:18">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:17">
+        <v>36</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:18">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" s="1">
         <v>1401</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="H5" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" s="1">
         <v>2</v>
       </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="1">
+      <c r="J5" s="1">
+        <v>2</v>
+      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="1">
         <v>10</v>
       </c>
-      <c r="M5" s="1">
-        <v>1</v>
-      </c>
       <c r="N5" s="1">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1">
         <v>10</v>
       </c>
-      <c r="O5" s="1">
-        <v>0</v>
-      </c>
       <c r="P5" s="1">
         <v>0</v>
       </c>
       <c r="Q5" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="1:17">
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:18">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E6" s="1">
         <v>1402</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
         <v>2</v>
       </c>
-      <c r="I6" s="1">
-        <v>1</v>
-      </c>
-      <c r="J6" s="1"/>
+      <c r="J6" s="1">
+        <v>1</v>
+      </c>
       <c r="K6" s="1"/>
-      <c r="L6" s="1">
+      <c r="L6" s="1"/>
+      <c r="M6" s="1">
         <v>10</v>
       </c>
-      <c r="M6" s="1">
-        <v>0</v>
-      </c>
       <c r="N6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="1">
         <v>0</v>
@@ -1816,44 +1952,47 @@
       <c r="Q6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:17">
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:18">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E7" s="1">
         <v>1403</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
         <v>2</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>5</v>
       </c>
-      <c r="J7" s="1"/>
       <c r="K7" s="1"/>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
+      <c r="L7" s="1"/>
       <c r="M7" s="1">
         <v>0</v>
       </c>
       <c r="N7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="1">
         <v>0</v>
@@ -1861,46 +2000,49 @@
       <c r="Q7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:17">
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:18">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E8" s="1">
         <v>1404</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
+        <v>49</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="H8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1">
+      <c r="J8" s="1">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1">
         <v>8</v>
       </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
       <c r="N8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="1">
         <v>0</v>
@@ -1908,46 +2050,49 @@
       <c r="Q8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:17">
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:18">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E9" s="1">
         <v>1405</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="1">
         <v>1</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
+      <c r="J9" s="1">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="1"/>
       <c r="M9" s="1">
         <v>0</v>
       </c>
       <c r="N9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="1">
         <v>0</v>
@@ -1955,46 +2100,49 @@
       <c r="Q9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="1:17">
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:18">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>6</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E10" s="1">
         <v>1406</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
         <v>2</v>
       </c>
-      <c r="I10" s="1">
-        <v>1</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1">
+      <c r="J10" s="1">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1">
         <v>4</v>
       </c>
-      <c r="M10" s="1">
-        <v>0</v>
-      </c>
       <c r="N10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" s="1">
         <v>0</v>
@@ -2002,89 +2150,95 @@
       <c r="Q10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" spans="1:17">
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:18">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>7</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E11" s="1">
         <v>1407</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
         <v>2</v>
       </c>
-      <c r="I11" s="1">
-        <v>1</v>
-      </c>
-      <c r="J11" s="1"/>
+      <c r="J11" s="1">
+        <v>1</v>
+      </c>
       <c r="K11" s="1"/>
-      <c r="L11" s="1">
+      <c r="L11" s="1"/>
+      <c r="M11" s="1">
         <v>6</v>
       </c>
-      <c r="M11" s="1">
-        <v>0</v>
-      </c>
       <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
         <v>2</v>
       </c>
-      <c r="O11" s="1">
-        <v>0</v>
-      </c>
       <c r="P11" s="1">
         <v>0</v>
       </c>
       <c r="Q11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="1:17">
+      <c r="R11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:18">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>8</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E12" s="1">
         <v>1408</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="H12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
       </c>
-      <c r="J12" s="1"/>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
       <c r="K12" s="1"/>
-      <c r="L12" s="1">
+      <c r="L12" s="1"/>
+      <c r="M12" s="1">
         <v>5</v>
       </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
       <c r="N12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="1">
         <v>0</v>
@@ -2092,44 +2246,47 @@
       <c r="Q12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" spans="1:17">
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:18">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>9</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E13" s="1">
         <v>1409</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
+        <v>67</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
         <v>2</v>
       </c>
-      <c r="I13" s="1">
-        <v>1</v>
-      </c>
-      <c r="J13" s="1"/>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
       <c r="K13" s="1"/>
-      <c r="L13" s="1">
+      <c r="L13" s="1"/>
+      <c r="M13" s="1">
         <v>2</v>
       </c>
-      <c r="M13" s="1">
-        <v>0</v>
-      </c>
       <c r="N13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" s="1">
         <v>0</v>
@@ -2137,46 +2294,49 @@
       <c r="Q13" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" spans="1:17">
+      <c r="R13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:18">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>10</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E14" s="1">
         <v>1410</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="H14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="1">
+        <v>1</v>
+      </c>
+      <c r="J14" s="1">
         <v>5</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
+      <c r="K14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L14" s="1"/>
       <c r="M14" s="1">
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" s="1">
         <v>0</v>
@@ -2184,44 +2344,47 @@
       <c r="Q14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" spans="1:17">
+      <c r="R14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:18">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>21</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E15" s="1">
         <v>1407</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
+        <v>74</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="H15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="1">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1">
         <v>5</v>
       </c>
-      <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
+      <c r="L15" s="1"/>
       <c r="M15" s="1">
         <v>0</v>
       </c>
       <c r="N15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" s="1">
         <v>0</v>
@@ -2229,46 +2392,49 @@
       <c r="Q15" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" spans="1:17">
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:18">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>22</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E16" s="1">
         <v>10002</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
+        <v>77</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="H16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1">
-        <v>0</v>
-      </c>
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L16" s="1"/>
       <c r="M16" s="1">
         <v>0</v>
       </c>
       <c r="N16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" s="1">
         <v>0</v>
@@ -2276,46 +2442,49 @@
       <c r="Q16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" spans="1:17">
+      <c r="R16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:18">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>23</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E17" s="1">
         <v>10001</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
+        <v>81</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="H17" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" s="1">
         <v>2</v>
       </c>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="L17" s="1">
+      <c r="J17" s="1">
+        <v>2</v>
+      </c>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M17" s="1">
         <v>4</v>
       </c>
-      <c r="M17" s="1">
+      <c r="N17" s="1">
         <v>0.5</v>
       </c>
-      <c r="N17" s="1">
-        <v>1</v>
-      </c>
       <c r="O17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="1">
         <v>0</v>
@@ -2323,46 +2492,49 @@
       <c r="Q17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17">
+      <c r="R17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:18">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>24</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E18" s="1">
         <v>15008</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="H18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="1">
         <v>1</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1">
-        <v>0</v>
-      </c>
+      <c r="J18" s="1">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L18" s="1"/>
       <c r="M18" s="1">
         <v>0</v>
       </c>
       <c r="N18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" s="1">
         <v>0</v>
@@ -2370,46 +2542,49 @@
       <c r="Q18" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" spans="1:17">
+      <c r="R18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:18">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>25</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="E19" s="1">
         <v>15015</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
+        <v>89</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="H19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" s="1">
+        <v>1</v>
+      </c>
+      <c r="J19" s="1">
         <v>5</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1">
-        <v>0</v>
-      </c>
+      <c r="K19" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L19" s="1"/>
       <c r="M19" s="1">
         <v>0</v>
       </c>
       <c r="N19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" s="1">
         <v>0</v>
@@ -2417,46 +2592,49 @@
       <c r="Q19" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" spans="1:17">
+      <c r="R19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:18">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>28</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E20" s="1">
         <v>1411</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="H20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="1">
         <v>1</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1">
-        <v>0</v>
-      </c>
+      <c r="J20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L20" s="1"/>
       <c r="M20" s="1">
         <v>0</v>
       </c>
       <c r="N20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" s="1">
         <v>0</v>
@@ -2464,46 +2642,49 @@
       <c r="Q20" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" spans="1:17">
+      <c r="R20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:18">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>2001</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="E21" s="1">
         <v>10001</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
+        <v>96</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="H21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="1">
         <v>1</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1">
+      <c r="J21" s="1">
+        <v>1</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1">
         <v>8</v>
       </c>
-      <c r="M21" s="1">
-        <v>0</v>
-      </c>
       <c r="N21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" s="1">
         <v>0</v>
@@ -2511,46 +2692,49 @@
       <c r="Q21" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" spans="1:17">
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:18">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>2002</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="E22" s="1">
         <v>10002</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="H22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="1">
         <v>1</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1">
+      <c r="J22" s="1">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1">
         <v>10</v>
       </c>
-      <c r="M22" s="1">
-        <v>0</v>
-      </c>
       <c r="N22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" s="1">
         <v>0</v>
@@ -2558,46 +2742,49 @@
       <c r="Q22" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" spans="1:17">
+      <c r="R22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="1:18">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>2003</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="E23" s="1">
         <v>10003</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
+        <v>104</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="H23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="1">
         <v>1</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1">
+      <c r="J23" s="1">
+        <v>1</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1">
         <v>8</v>
       </c>
-      <c r="M23" s="1">
-        <v>0</v>
-      </c>
       <c r="N23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" s="1">
         <v>0</v>
@@ -2605,46 +2792,49 @@
       <c r="Q23" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" spans="1:17">
+      <c r="R23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:18">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>2004</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="E24" s="1">
         <v>10004</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
+        <v>108</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="H24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="1">
         <v>1</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1">
+      <c r="J24" s="1">
+        <v>1</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1">
         <v>10</v>
       </c>
-      <c r="M24" s="1">
-        <v>0</v>
-      </c>
       <c r="N24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" s="1">
         <v>0</v>
@@ -2652,46 +2842,49 @@
       <c r="Q24" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" spans="1:17">
+      <c r="R24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:18">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>3001</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="E25" s="1">
         <v>10101</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
+        <v>112</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1">
         <v>2</v>
       </c>
-      <c r="I25" s="1">
-        <v>1</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1">
+      <c r="J25" s="1">
+        <v>1</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1">
         <v>2</v>
       </c>
-      <c r="M25" s="1">
-        <v>0</v>
-      </c>
       <c r="N25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" s="1">
         <v>0</v>
@@ -2699,46 +2892,49 @@
       <c r="Q25" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" spans="1:17">
+      <c r="R25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:18">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>3002</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="E26" s="1">
         <v>10102</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
+        <v>116</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1">
         <v>2</v>
       </c>
-      <c r="I26" s="1">
+      <c r="J26" s="1">
         <v>4</v>
       </c>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="L26" s="1">
+      <c r="K26" s="1"/>
+      <c r="L26" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M26" s="1">
         <v>0.8</v>
       </c>
-      <c r="M26" s="1">
-        <v>0</v>
-      </c>
       <c r="N26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" s="1">
         <v>0</v>
@@ -2746,46 +2942,49 @@
       <c r="Q26" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" spans="1:17">
+      <c r="R26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:18">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>3003</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="E27" s="1">
         <v>10103</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0</v>
+        <v>120</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="H27" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I27" s="1">
         <v>2</v>
       </c>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L27" s="1">
+      <c r="J27" s="1">
+        <v>2</v>
+      </c>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M27" s="1">
         <v>6</v>
       </c>
-      <c r="M27" s="1">
-        <v>1</v>
-      </c>
       <c r="N27" s="1">
         <v>1</v>
       </c>
       <c r="O27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" s="1">
         <v>0</v>
@@ -2793,46 +2992,49 @@
       <c r="Q27" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" spans="1:17">
+      <c r="R27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="1:18">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>4001</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="E28" s="1">
         <v>10201</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0</v>
+        <v>124</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="H28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="1">
         <v>1</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1">
+      <c r="J28" s="1">
+        <v>1</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1">
         <v>10</v>
       </c>
-      <c r="M28" s="1">
-        <v>0</v>
-      </c>
       <c r="N28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" s="1">
         <v>0</v>
@@ -2840,48 +3042,51 @@
       <c r="Q28" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" spans="1:17">
+      <c r="R28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="1:18">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>4002</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="E29" s="1">
         <v>10202</v>
       </c>
       <c r="F29" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1">
+        <v>1</v>
+      </c>
+      <c r="J29" s="1">
+        <v>5</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G29" s="1">
-        <v>0</v>
-      </c>
-      <c r="H29" s="1">
-        <v>1</v>
-      </c>
-      <c r="I29" s="1">
-        <v>5</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="L29" s="1">
-        <v>0</v>
+      <c r="L29" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="M29" s="1">
         <v>0</v>
       </c>
       <c r="N29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" s="1">
         <v>0</v>
@@ -2889,44 +3094,45 @@
       <c r="Q29" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" spans="1:17">
+      <c r="R29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" spans="1:18">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>4003</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="E30" s="1">
         <v>10203</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="G30" s="1"/>
       <c r="H30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" s="1">
+        <v>1</v>
+      </c>
+      <c r="J30" s="1">
         <v>5</v>
       </c>
-      <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-      <c r="L30" s="1">
-        <v>0</v>
-      </c>
+      <c r="L30" s="1"/>
       <c r="M30" s="1">
         <v>0</v>
       </c>
       <c r="N30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" s="1">
         <v>0</v>
@@ -2934,46 +3140,49 @@
       <c r="Q30" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" spans="1:17">
+      <c r="R30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" spans="1:18">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
         <v>5001</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="E31" s="1">
         <v>15001</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G31" s="1">
-        <v>0</v>
+        <v>134</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="H31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="1">
+        <v>1</v>
+      </c>
+      <c r="J31" s="1">
         <v>3</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1">
+      <c r="K31" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1">
         <v>30</v>
       </c>
-      <c r="M31" s="1">
-        <v>0</v>
-      </c>
       <c r="N31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" s="1">
         <v>0</v>
@@ -2981,46 +3190,49 @@
       <c r="Q31" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" spans="1:17">
+      <c r="R31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" spans="1:18">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
         <v>5003</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="E32" s="1">
         <v>15003</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
+        <v>138</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="H32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" s="1">
         <v>1</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1">
+      <c r="J32" s="1">
+        <v>1</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1">
         <v>8</v>
       </c>
-      <c r="M32" s="1">
-        <v>0</v>
-      </c>
       <c r="N32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P32" s="1">
         <v>0</v>
@@ -3028,46 +3240,49 @@
       <c r="Q32" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" spans="1:17">
+      <c r="R32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" spans="1:18">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
         <v>5005</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="E33" s="1">
         <v>15005</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0</v>
+        <v>141</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1">
         <v>2</v>
       </c>
-      <c r="I33" s="1">
+      <c r="J33" s="1">
         <v>4</v>
       </c>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="L33" s="1">
+      <c r="K33" s="1"/>
+      <c r="L33" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M33" s="1">
         <v>2</v>
       </c>
-      <c r="M33" s="1">
-        <v>0</v>
-      </c>
       <c r="N33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" s="1">
         <v>0</v>
@@ -3075,46 +3290,49 @@
       <c r="Q33" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" spans="1:17">
+      <c r="R33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" spans="1:18">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
         <v>5007</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="E34" s="1">
         <v>15007</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G34" s="1">
-        <v>0</v>
+        <v>144</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="1">
         <v>2</v>
       </c>
-      <c r="I34" s="1">
+      <c r="J34" s="1">
         <v>4</v>
       </c>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="L34" s="1">
+      <c r="K34" s="1"/>
+      <c r="L34" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="M34" s="1">
         <v>3</v>
       </c>
-      <c r="M34" s="1">
-        <v>0</v>
-      </c>
       <c r="N34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34" s="1">
         <v>0</v>
@@ -3122,46 +3340,49 @@
       <c r="Q34" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" spans="1:17">
+      <c r="R34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" spans="1:18">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
         <v>5008</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="E35" s="1">
         <v>15008</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G35" s="1">
-        <v>0</v>
+        <v>148</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="H35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="1">
         <v>1</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1">
+      <c r="J35" s="1">
+        <v>1</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1">
         <v>10</v>
       </c>
-      <c r="M35" s="1">
-        <v>0</v>
-      </c>
       <c r="N35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35" s="1">
         <v>0</v>
@@ -3169,46 +3390,49 @@
       <c r="Q35" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" spans="1:17">
+      <c r="R35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" spans="1:18">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
         <v>5009</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="E36" s="1">
         <v>15009</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36" s="1">
         <v>2</v>
       </c>
-      <c r="I36" s="1">
+      <c r="J36" s="1">
         <v>4</v>
       </c>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="L36" s="1">
+      <c r="K36" s="1"/>
+      <c r="L36" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M36" s="1">
         <v>4</v>
       </c>
-      <c r="M36" s="1">
-        <v>0</v>
-      </c>
       <c r="N36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36" s="1">
         <v>0</v>
@@ -3216,46 +3440,49 @@
       <c r="Q36" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" spans="1:17">
+      <c r="R36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" spans="1:18">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
         <v>5011</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1" t="s">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="E37" s="1">
         <v>15011</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0</v>
+        <v>156</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="H37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="1">
+        <v>1</v>
+      </c>
+      <c r="J37" s="1">
         <v>5</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1">
+      <c r="K37" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1">
         <v>10</v>
       </c>
-      <c r="M37" s="1">
-        <v>0</v>
-      </c>
       <c r="N37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37" s="1">
         <v>0</v>
@@ -3263,46 +3490,49 @@
       <c r="Q37" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" spans="1:17">
+      <c r="R37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" spans="1:18">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
         <v>5012</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="E38" s="1">
         <v>15012</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0</v>
+        <v>160</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="H38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="1">
         <v>1</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1">
+      <c r="J38" s="1">
+        <v>1</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1">
         <v>10</v>
       </c>
-      <c r="M38" s="1">
-        <v>0</v>
-      </c>
       <c r="N38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P38" s="1">
         <v>0</v>
@@ -3310,46 +3540,49 @@
       <c r="Q38" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" spans="1:17">
+      <c r="R38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" spans="1:18">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
         <v>5013</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1" t="s">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="E39" s="1">
         <v>15013</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0</v>
+        <v>164</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="H39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" s="1">
+        <v>1</v>
+      </c>
+      <c r="J39" s="1">
         <v>2</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1">
+      <c r="K39" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1">
         <v>15</v>
       </c>
-      <c r="M39" s="1">
+      <c r="N39" s="1">
         <v>3</v>
       </c>
-      <c r="N39" s="1">
-        <v>1</v>
-      </c>
       <c r="O39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39" s="1">
         <v>0</v>
@@ -3357,46 +3590,49 @@
       <c r="Q39" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" spans="1:17">
+      <c r="R39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" spans="1:18">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
         <v>5014</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="E40" s="1">
         <v>15014</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G40" s="1">
-        <v>0</v>
+        <v>168</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="H40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="1">
         <v>1</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1">
+      <c r="J40" s="1">
+        <v>1</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1">
         <v>15</v>
       </c>
-      <c r="M40" s="1">
-        <v>0</v>
-      </c>
       <c r="N40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P40" s="1">
         <v>0</v>
@@ -3404,46 +3640,49 @@
       <c r="Q40" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" spans="1:17">
+      <c r="R40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" spans="1:18">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
         <v>5015</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="E41" s="1">
         <v>15015</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G41" s="1">
-        <v>0</v>
+        <v>172</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="H41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" s="1">
+        <v>1</v>
+      </c>
+      <c r="J41" s="1">
         <v>5</v>
       </c>
-      <c r="J41" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1">
-        <v>0</v>
-      </c>
+      <c r="K41" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="L41" s="1"/>
       <c r="M41" s="1">
         <v>0</v>
       </c>
       <c r="N41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P41" s="1">
         <v>0</v>
@@ -3451,46 +3690,49 @@
       <c r="Q41" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" spans="1:17">
+      <c r="R41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" spans="1:18">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
         <v>5017</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="E42" s="1">
         <v>15017</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0</v>
+        <v>176</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>177</v>
       </c>
       <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1">
         <v>2</v>
       </c>
-      <c r="I42" s="1">
-        <v>1</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1">
+      <c r="J42" s="1">
+        <v>1</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1">
         <v>15</v>
       </c>
-      <c r="M42" s="1">
-        <v>0</v>
-      </c>
       <c r="N42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P42" s="1">
         <v>0</v>
@@ -3498,46 +3740,49 @@
       <c r="Q42" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" spans="1:17">
+      <c r="R42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" spans="1:18">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
         <v>5018</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="E43" s="1">
         <v>15018</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G43" s="1">
-        <v>0</v>
+        <v>180</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1">
         <v>2</v>
       </c>
-      <c r="I43" s="1">
-        <v>1</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1">
+      <c r="J43" s="1">
+        <v>1</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1">
         <v>15</v>
       </c>
-      <c r="M43" s="1">
-        <v>0</v>
-      </c>
       <c r="N43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P43" s="1">
         <v>0</v>
@@ -3545,46 +3790,49 @@
       <c r="Q43" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" spans="1:17">
+      <c r="R43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" spans="1:18">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
         <v>5019</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1" t="s">
-        <v>143</v>
+        <v>183</v>
       </c>
       <c r="E44" s="1">
         <v>15019</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0</v>
+        <v>184</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1">
         <v>2</v>
       </c>
-      <c r="I44" s="1">
+      <c r="J44" s="1">
         <v>4</v>
       </c>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="L44" s="1">
+      <c r="K44" s="1"/>
+      <c r="L44" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="M44" s="1">
         <v>10</v>
       </c>
-      <c r="M44" s="1">
-        <v>0</v>
-      </c>
       <c r="N44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44" s="1">
         <v>0</v>
@@ -3592,46 +3840,49 @@
       <c r="Q44" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" spans="1:17">
+      <c r="R44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" spans="1:18">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
         <v>5020</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="E45" s="1">
         <v>15020</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="G45" s="1">
-        <v>0</v>
+        <v>188</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1">
         <v>2</v>
       </c>
-      <c r="I45" s="1">
+      <c r="J45" s="1">
         <v>4</v>
       </c>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="L45" s="1">
+      <c r="K45" s="1"/>
+      <c r="L45" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="M45" s="1">
         <v>10</v>
       </c>
-      <c r="M45" s="1">
-        <v>0</v>
-      </c>
       <c r="N45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P45" s="1">
         <v>0</v>
@@ -3639,46 +3890,49 @@
       <c r="Q45" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" spans="1:17">
+      <c r="R45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" spans="1:18">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
         <v>5021</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="E46" s="1">
         <v>15021</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="G46" s="1">
-        <v>0</v>
+        <v>192</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="H46" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I46" s="1">
         <v>2</v>
       </c>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="L46" s="1">
+      <c r="J46" s="1">
+        <v>2</v>
+      </c>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="M46" s="1">
         <v>15</v>
       </c>
-      <c r="M46" s="1">
-        <v>1</v>
-      </c>
       <c r="N46" s="1">
         <v>1</v>
       </c>
       <c r="O46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P46" s="1">
         <v>0</v>
@@ -3686,46 +3940,47 @@
       <c r="Q46" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" spans="1:17">
+      <c r="R46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" spans="1:18">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
         <v>6001</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="E47" s="1">
         <v>0</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G47" s="1">
-        <v>1</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="G47" s="1"/>
       <c r="H47" s="1">
         <v>1</v>
       </c>
       <c r="I47" s="1">
         <v>1</v>
       </c>
-      <c r="J47" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1">
-        <v>0</v>
-      </c>
+      <c r="J47" s="1">
+        <v>1</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="L47" s="1"/>
       <c r="M47" s="1">
         <v>0</v>
       </c>
       <c r="N47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P47" s="1">
         <v>0</v>
@@ -3733,44 +3988,45 @@
       <c r="Q47" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" ht="15" customHeight="1" spans="1:17">
+      <c r="R47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1" spans="1:18">
       <c r="A48" s="1"/>
       <c r="B48" s="1">
         <v>6002</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1" t="s">
-        <v>155</v>
+        <v>198</v>
       </c>
       <c r="E48" s="1">
         <v>0</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="G48" s="1">
-        <v>1</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="G48" s="1"/>
       <c r="H48" s="1">
         <v>1</v>
       </c>
       <c r="I48" s="1">
+        <v>1</v>
+      </c>
+      <c r="J48" s="1">
         <v>5</v>
       </c>
-      <c r="J48" s="1"/>
       <c r="K48" s="1"/>
-      <c r="L48" s="1">
-        <v>0</v>
-      </c>
+      <c r="L48" s="1"/>
       <c r="M48" s="1">
         <v>0</v>
       </c>
       <c r="N48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P48" s="1">
         <v>0</v>
@@ -3778,44 +4034,45 @@
       <c r="Q48" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" spans="1:17">
+      <c r="R48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" spans="1:18">
       <c r="A49" s="1"/>
       <c r="B49" s="1">
         <v>6003</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1" t="s">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="E49" s="1">
         <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G49" s="1">
-        <v>1</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="G49" s="1"/>
       <c r="H49" s="1">
         <v>1</v>
       </c>
       <c r="I49" s="1">
+        <v>1</v>
+      </c>
+      <c r="J49" s="1">
         <v>5</v>
       </c>
-      <c r="J49" s="1"/>
       <c r="K49" s="1"/>
-      <c r="L49" s="1">
-        <v>0</v>
-      </c>
+      <c r="L49" s="1"/>
       <c r="M49" s="1">
         <v>0</v>
       </c>
       <c r="N49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P49" s="1">
         <v>0</v>
@@ -3823,46 +4080,47 @@
       <c r="Q49" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" ht="15" customHeight="1" spans="1:17">
+      <c r="R49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1" spans="1:18">
       <c r="A50" s="1"/>
       <c r="B50" s="1">
         <v>6004</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1" t="s">
-        <v>159</v>
+        <v>202</v>
       </c>
       <c r="E50" s="1">
         <v>0</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="G50" s="1">
-        <v>1</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="G50" s="1"/>
       <c r="H50" s="1">
         <v>1</v>
       </c>
       <c r="I50" s="1">
         <v>1</v>
       </c>
-      <c r="J50" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1">
-        <v>0</v>
-      </c>
+      <c r="J50" s="1">
+        <v>1</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="L50" s="1"/>
       <c r="M50" s="1">
         <v>0</v>
       </c>
       <c r="N50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" s="1">
         <v>0</v>
@@ -3870,46 +4128,47 @@
       <c r="Q50" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" ht="15" customHeight="1" spans="1:17">
+      <c r="R50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1" spans="1:18">
       <c r="A51" s="1"/>
       <c r="B51" s="1">
         <v>6005</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1" t="s">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="E51" s="1">
         <v>0</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G51" s="1">
-        <v>1</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="G51" s="1"/>
       <c r="H51" s="1">
         <v>1</v>
       </c>
       <c r="I51" s="1">
         <v>1</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1">
-        <v>0</v>
-      </c>
+      <c r="J51" s="1">
+        <v>1</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="L51" s="1"/>
       <c r="M51" s="1">
         <v>0</v>
       </c>
       <c r="N51" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P51" s="1">
         <v>0</v>
@@ -3917,46 +4176,47 @@
       <c r="Q51" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" ht="15" customHeight="1" spans="1:17">
+      <c r="R51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1" spans="1:18">
       <c r="A52" s="1"/>
       <c r="B52" s="1">
         <v>6006</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
       <c r="E52" s="1">
         <v>0</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="G52" s="1">
-        <v>1</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="G52" s="1"/>
       <c r="H52" s="1">
         <v>1</v>
       </c>
       <c r="I52" s="1">
         <v>1</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1">
-        <v>0</v>
-      </c>
+      <c r="J52" s="1">
+        <v>1</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="L52" s="1"/>
       <c r="M52" s="1">
         <v>0</v>
       </c>
       <c r="N52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P52" s="1">
         <v>0</v>
@@ -3964,46 +4224,47 @@
       <c r="Q52" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" ht="15" customHeight="1" spans="1:17">
+      <c r="R52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1" spans="1:18">
       <c r="A53" s="1"/>
       <c r="B53" s="1">
         <v>6007</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
-        <v>168</v>
+        <v>211</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G53" s="1">
-        <v>1</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="G53" s="1"/>
       <c r="H53" s="1">
         <v>1</v>
       </c>
       <c r="I53" s="1">
         <v>1</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1">
-        <v>0</v>
-      </c>
+      <c r="J53" s="1">
+        <v>1</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="L53" s="1"/>
       <c r="M53" s="1">
         <v>0</v>
       </c>
       <c r="N53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P53" s="1">
         <v>0</v>
@@ -4011,46 +4272,47 @@
       <c r="Q53" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" ht="15" customHeight="1" spans="1:17">
+      <c r="R53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1" spans="1:18">
       <c r="A54" s="1"/>
       <c r="B54" s="1">
         <v>6008</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1" t="s">
-        <v>171</v>
+        <v>214</v>
       </c>
       <c r="E54" s="1">
         <v>0</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G54" s="1">
-        <v>1</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="G54" s="1"/>
       <c r="H54" s="1">
         <v>1</v>
       </c>
       <c r="I54" s="1">
         <v>1</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1">
-        <v>0</v>
-      </c>
+      <c r="J54" s="1">
+        <v>1</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="L54" s="1"/>
       <c r="M54" s="1">
         <v>0</v>
       </c>
       <c r="N54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P54" s="1">
         <v>0</v>
@@ -4058,51 +4320,55 @@
       <c r="Q54" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" ht="15" customHeight="1" spans="1:17">
+      <c r="R54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1" spans="1:18">
       <c r="A55" s="1"/>
       <c r="B55" s="1">
         <v>6009</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="E55" s="1">
         <v>0</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G55" s="1">
-        <v>1</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="G55" s="1"/>
       <c r="H55" s="1">
         <v>1</v>
       </c>
       <c r="I55" s="1">
         <v>1</v>
       </c>
-      <c r="J55" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1">
-        <v>0</v>
-      </c>
+      <c r="J55" s="1">
+        <v>1</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="L55" s="1"/>
       <c r="M55" s="1">
         <v>0</v>
       </c>
       <c r="N55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P55" s="1">
         <v>0</v>
       </c>
       <c r="Q55" s="1">
+        <v>0</v>
+      </c>
+      <c r="R55" s="1">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/BuffTable.xlsx
+++ b/AAAGameData/DataTables/BuffTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="15300"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -431,13 +431,13 @@
     <t>神圣庇护</t>
   </si>
   <si>
-    <t>提供1000点护盾，持续30秒</t>
+    <t>提供300点护盾，持续30秒</t>
   </si>
   <si>
     <t>神明的庇护凝聚成盾，能够抵挡一切伤害。</t>
   </si>
   <si>
-    <t>{"Shield":1000}</t>
+    <t>{"Shield":300}</t>
   </si>
   <si>
     <t>战争号角</t>
@@ -1652,15 +1652,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="75.7777777777778" customWidth="1"/>
-    <col min="7" max="7" width="50.7777777777778" customWidth="1"/>
+    <col min="6" max="6" width="75.775" customWidth="1"/>
+    <col min="7" max="7" width="50.775" customWidth="1"/>
     <col min="8" max="8" width="34" customWidth="1"/>
     <col min="9" max="9" width="48" customWidth="1"/>
     <col min="10" max="14" width="50" customWidth="1"/>
@@ -1802,7 +1802,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" ht="57.6" spans="1:18">
+    <row r="4" ht="54" spans="1:18">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
